--- a/Design Files/MainBoard_2.0/Main_Board_2.0/BOM/eSpark-BOM_Main_Board_2.0.xlsx
+++ b/Design Files/MainBoard_2.0/Main_Board_2.0/BOM/eSpark-BOM_Main_Board_2.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="413">
   <si>
     <t>Component list</t>
   </si>
@@ -172,30 +172,15 @@
     <t>R2</t>
   </si>
   <si>
-    <t>R3, R5, R15, R16, R38</t>
-  </si>
-  <si>
-    <t>R4, R9, R12, R14, R21, R22, R23, R28, R29, R30, R31, R32, R33, R34, R35, R36, R37, R40, R41, R42, R45, R49, R55, R58</t>
-  </si>
-  <si>
     <t>R7</t>
   </si>
   <si>
-    <t>R10</t>
-  </si>
-  <si>
-    <t>R11</t>
-  </si>
-  <si>
     <t>R13</t>
   </si>
   <si>
     <t>R17</t>
   </si>
   <si>
-    <t>R18, R19, R20, R39</t>
-  </si>
-  <si>
     <t>R24, R25, R26, R27</t>
   </si>
   <si>
@@ -367,12 +352,6 @@
     <t>RES 0.01 OHM 1% 1W 1206</t>
   </si>
   <si>
-    <t>RES SMD 402K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>RES SMD 100K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
     <t>RES 20K OHM 1% 1/10W 0603</t>
   </si>
   <si>
@@ -658,9 +637,6 @@
     <t>PA1206FRE470R01Z</t>
   </si>
   <si>
-    <t>CRCW0603402KFKEA</t>
-  </si>
-  <si>
     <t>RC0603FR-0720KL</t>
   </si>
   <si>
@@ -775,9 +751,6 @@
     <t>TECH PUBLIC</t>
   </si>
   <si>
-    <t>Vishay</t>
-  </si>
-  <si>
     <t>Vishay Dale</t>
   </si>
   <si>
@@ -886,12 +859,6 @@
     <t>10mR</t>
   </si>
   <si>
-    <t>402K</t>
-  </si>
-  <si>
-    <t>100K</t>
-  </si>
-  <si>
     <t>20K</t>
   </si>
   <si>
@@ -1144,9 +1111,6 @@
     <t>Total Cost (1 Boards)</t>
   </si>
   <si>
-    <t>CRCW0603100KFKEA</t>
-  </si>
-  <si>
     <t>1.02000</t>
   </si>
   <si>
@@ -1265,6 +1229,36 @@
   </si>
   <si>
     <t>Waveshare</t>
+  </si>
+  <si>
+    <t>C1, C46, C47, C51, C53, C79, C80, C96, C97, C98, C99, C104, C105, C107, C109</t>
+  </si>
+  <si>
+    <t>Diode</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>1A Single 50V 1.1V@1A SMA(DO-214AC) Diodes - General Purpose ROHS</t>
+  </si>
+  <si>
+    <t>SMA(DO-214AC)</t>
+  </si>
+  <si>
+    <t>1N4001</t>
+  </si>
+  <si>
+    <t>TWGMC</t>
+  </si>
+  <si>
+    <t>R4, R9, R10, R14, R21, R22, R23, R28, R29, R30, R31, R32, R33, R34, R35, R36, R37, R40, R41, R42, R45, R49, R55, R58</t>
+  </si>
+  <si>
+    <t>R3, R5, R11, R15, R16, R38</t>
+  </si>
+  <si>
+    <t>R12, R18, R19, R20, R39</t>
   </si>
 </sst>
 </file>
@@ -1898,6 +1892,9 @@
     <xf numFmtId="165" fontId="16" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1920,9 +1917,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2320,7 +2314,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:P92"/>
+  <dimension ref="A1:P91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="10" customWidth="1"/>
@@ -2349,14 +2343,14 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="74"/>
     </row>
     <row r="2" spans="1:16" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2367,7 +2361,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="38" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="3"/>
@@ -2378,7 +2372,7 @@
       <c r="M2" s="30"/>
       <c r="N2" s="30"/>
       <c r="O2" s="30"/>
-      <c r="P2" s="76"/>
+      <c r="P2" s="77"/>
     </row>
     <row r="3" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -2389,7 +2383,7 @@
       </c>
       <c r="E3" s="26"/>
       <c r="F3" s="39" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="G3" s="28"/>
       <c r="H3" s="29"/>
@@ -2400,7 +2394,7 @@
       <c r="M3" s="23"/>
       <c r="N3" s="23"/>
       <c r="O3" s="23"/>
-      <c r="P3" s="77"/>
+      <c r="P3" s="78"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2418,7 +2412,7 @@
       <c r="M4" s="23"/>
       <c r="N4" s="23"/>
       <c r="O4" s="23"/>
-      <c r="P4" s="77"/>
+      <c r="P4" s="78"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2436,7 +2430,7 @@
       <c r="M5" s="33"/>
       <c r="N5" s="33"/>
       <c r="O5" s="33"/>
-      <c r="P5" s="77"/>
+      <c r="P5" s="78"/>
     </row>
     <row r="6" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -2454,7 +2448,7 @@
       <c r="M6" s="33"/>
       <c r="N6" s="33"/>
       <c r="O6" s="33"/>
-      <c r="P6" s="78"/>
+      <c r="P6" s="79"/>
     </row>
     <row r="7" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -2468,40 +2462,40 @@
         <v>20</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="I7" s="40" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="24" x14ac:dyDescent="0.25">
@@ -2517,19 +2511,19 @@
         <v>21</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I8" s="41" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="J8" s="14">
         <v>14</v>
@@ -2539,10 +2533,10 @@
         <v>70</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="N8" s="15">
         <f>M8*K8</f>
@@ -2554,7 +2548,7 @@
     <row r="9" spans="1:16" ht="36" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="16">
-        <f t="shared" ref="B9:B72" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B71" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="22" t="s">
@@ -2564,19 +2558,19 @@
         <v>22</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I9" s="42" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="J9" s="20">
         <v>20</v>
@@ -2586,13 +2580,13 @@
         <v>100</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="N9" s="15">
-        <f t="shared" ref="N9:N77" si="2">M9*K9</f>
+        <f t="shared" ref="N9:N76" si="2">M9*K9</f>
         <v>29.970000000000002</v>
       </c>
       <c r="O9" s="20"/>
@@ -2611,19 +2605,19 @@
         <v>23</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I10" s="41" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="J10" s="14">
         <v>10</v>
@@ -2633,10 +2627,10 @@
         <v>50</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="N10" s="15">
         <f t="shared" si="2"/>
@@ -2658,19 +2652,19 @@
         <v>24</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I11" s="42" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="J11" s="20">
         <v>4</v>
@@ -2680,10 +2674,10 @@
         <v>20</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="N11" s="15">
         <f t="shared" si="2"/>
@@ -2705,19 +2699,19 @@
         <v>25</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I12" s="41" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="J12" s="14">
         <v>8</v>
@@ -2727,10 +2721,10 @@
         <v>40</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M12" s="15" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="N12" s="15">
         <f t="shared" si="2"/>
@@ -2752,19 +2746,19 @@
         <v>26</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I13" s="42" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="J13" s="20">
         <v>2</v>
@@ -2774,10 +2768,10 @@
         <v>10</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M13" s="15" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="N13" s="15">
         <f t="shared" si="2"/>
@@ -2799,19 +2793,19 @@
         <v>27</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="J14" s="14">
         <v>2</v>
@@ -2821,10 +2815,10 @@
         <v>10</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="N14" s="15">
         <f t="shared" si="2"/>
@@ -2846,19 +2840,19 @@
         <v>28</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I15" s="42" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="J15" s="20">
         <v>1</v>
@@ -2868,10 +2862,10 @@
         <v>5</v>
       </c>
       <c r="L15" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="N15" s="15">
         <f t="shared" si="2"/>
@@ -2893,19 +2887,19 @@
         <v>29</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="J16" s="14">
         <v>11</v>
@@ -2915,10 +2909,10 @@
         <v>55</v>
       </c>
       <c r="L16" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="N16" s="15">
         <f t="shared" si="2"/>
@@ -2940,19 +2934,19 @@
         <v>30</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I17" s="42" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="J17" s="20">
         <v>23</v>
@@ -2962,10 +2956,10 @@
         <v>115</v>
       </c>
       <c r="L17" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="N17" s="15">
         <f t="shared" si="2"/>
@@ -2987,19 +2981,19 @@
         <v>31</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="I18" s="41" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="J18" s="14">
         <v>4</v>
@@ -3009,10 +3003,10 @@
         <v>20</v>
       </c>
       <c r="L18" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M18" s="15" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="N18" s="15">
         <f t="shared" si="2"/>
@@ -3034,19 +3028,19 @@
         <v>32</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I19" s="42" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="J19" s="20">
         <v>2</v>
@@ -3056,10 +3050,10 @@
         <v>10</v>
       </c>
       <c r="L19" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M19" s="15" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="N19" s="15">
         <f t="shared" si="2"/>
@@ -3081,19 +3075,19 @@
         <v>33</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="I20" s="41" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="J20" s="14">
         <v>2</v>
@@ -3103,10 +3097,10 @@
         <v>10</v>
       </c>
       <c r="L20" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M20" s="15" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="N20" s="15">
         <f t="shared" si="2"/>
@@ -3128,19 +3122,19 @@
         <v>34</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I21" s="42" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="J21" s="20">
         <v>1</v>
@@ -3150,10 +3144,10 @@
         <v>5</v>
       </c>
       <c r="L21" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M21" s="15" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="N21" s="15">
         <f t="shared" si="2"/>
@@ -3172,22 +3166,22 @@
         <v>4</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="G22" s="41" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I22" s="41" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="J22" s="14">
         <v>1</v>
@@ -3197,7 +3191,7 @@
         <v>5</v>
       </c>
       <c r="L22" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M22" s="15">
         <v>0.37</v>
@@ -3222,19 +3216,19 @@
         <v>35</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="I23" s="41" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="J23" s="14">
         <v>2</v>
@@ -3244,10 +3238,10 @@
         <v>10</v>
       </c>
       <c r="L23" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M23" s="15" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="N23" s="15">
         <f t="shared" si="2"/>
@@ -3256,52 +3250,52 @@
       <c r="O23" s="14"/>
       <c r="P23" s="19"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="36" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="16">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="E24" s="41" t="s">
+        <v>406</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="G24" s="41" t="s">
+        <v>408</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="I24" s="41" t="s">
+        <v>301</v>
+      </c>
+      <c r="J24" s="14">
+        <v>1</v>
+      </c>
+      <c r="K24" s="14">
+        <f>J24*5</f>
         <v>5</v>
       </c>
-      <c r="D24" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="H24" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="I24" s="42" t="s">
-        <v>281</v>
-      </c>
-      <c r="J24" s="20">
-        <v>1</v>
-      </c>
-      <c r="K24" s="20">
-        <f t="shared" ref="K24" si="9">J24*5</f>
-        <v>5</v>
-      </c>
       <c r="L24" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="M24" s="15" t="s">
-        <v>328</v>
+        <v>368</v>
+      </c>
+      <c r="M24" s="15">
+        <v>6.7999999999999996E-3</v>
       </c>
       <c r="N24" s="15">
         <f t="shared" si="2"/>
-        <v>1.45</v>
-      </c>
-      <c r="O24" s="20"/>
-      <c r="P24" s="20"/>
+        <v>3.3999999999999996E-2</v>
+      </c>
+      <c r="O24" s="14"/>
+      <c r="P24" s="19"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
@@ -3309,93 +3303,93 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="I25" s="41" t="s">
-        <v>281</v>
-      </c>
-      <c r="J25" s="14">
-        <v>4</v>
-      </c>
-      <c r="K25" s="14">
-        <f>J25*5</f>
-        <v>20</v>
+      <c r="D25" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I25" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="J25" s="20">
+        <v>1</v>
+      </c>
+      <c r="K25" s="20">
+        <f t="shared" ref="K25" si="9">J25*5</f>
+        <v>5</v>
       </c>
       <c r="L25" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M25" s="15" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="N25" s="15">
         <f t="shared" si="2"/>
-        <v>3.62</v>
-      </c>
-      <c r="O25" s="14"/>
-      <c r="P25" s="19"/>
-    </row>
-    <row r="26" spans="1:16" ht="24" x14ac:dyDescent="0.25">
+        <v>1.45</v>
+      </c>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="16">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C26" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="41" t="s">
-        <v>395</v>
+      <c r="C26" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="G26" s="41" t="s">
-        <v>396</v>
+        <v>144</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>191</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>397</v>
+        <v>233</v>
       </c>
       <c r="I26" s="41" t="s">
-        <v>312</v>
+        <v>272</v>
       </c>
       <c r="J26" s="14">
-        <v>1</v>
-      </c>
-      <c r="K26" s="20">
-        <f t="shared" ref="K26" si="10">J26*5</f>
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="K26" s="14">
+        <f>J26*5</f>
+        <v>20</v>
       </c>
       <c r="L26" s="44" t="s">
-        <v>380</v>
-      </c>
-      <c r="M26" s="15">
-        <v>0.16089999999999999</v>
+        <v>360</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>331</v>
       </c>
       <c r="N26" s="15">
         <f t="shared" si="2"/>
-        <v>0.80449999999999999</v>
-      </c>
-      <c r="O26" s="20"/>
-      <c r="P26" s="20"/>
+        <v>3.62</v>
+      </c>
+      <c r="O26" s="14"/>
+      <c r="P26" s="19"/>
     </row>
     <row r="27" spans="1:16" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
@@ -3403,48 +3397,48 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C27" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="14" t="s">
+      <c r="C27" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>383</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="G27" s="41" t="s">
         <v>384</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>199</v>
-      </c>
       <c r="H27" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="I27" s="42" t="s">
-        <v>312</v>
+        <v>385</v>
+      </c>
+      <c r="I27" s="41" t="s">
+        <v>301</v>
       </c>
       <c r="J27" s="14">
         <v>1</v>
       </c>
-      <c r="K27" s="14">
-        <f>J27*5</f>
+      <c r="K27" s="20">
+        <f t="shared" ref="K27" si="10">J27*5</f>
         <v>5</v>
       </c>
       <c r="L27" s="44" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="M27" s="15">
-        <v>3.56E-2</v>
+        <v>0.16089999999999999</v>
       </c>
       <c r="N27" s="15">
         <f t="shared" si="2"/>
-        <v>0.17799999999999999</v>
-      </c>
-      <c r="O27" s="14"/>
-      <c r="P27" s="19"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.80449999999999999</v>
+      </c>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+    </row>
+    <row r="28" spans="1:16" ht="24" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="16">
         <f t="shared" si="0"/>
@@ -3454,22 +3448,22 @@
         <v>7</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>386</v>
+        <v>97</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>311</v>
+        <v>145</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>385</v>
+        <v>192</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="I28" s="42" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="J28" s="14">
         <v>1</v>
@@ -3479,14 +3473,14 @@
         <v>5</v>
       </c>
       <c r="L28" s="44" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="M28" s="15">
-        <v>0.99</v>
+        <v>3.56E-2</v>
       </c>
       <c r="N28" s="15">
         <f t="shared" si="2"/>
-        <v>4.95</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="O28" s="14"/>
       <c r="P28" s="19"/>
@@ -3497,46 +3491,46 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C29" s="22" t="s">
-        <v>398</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E29" s="42" t="s">
-        <v>399</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="G29" s="42" t="s">
-        <v>400</v>
-      </c>
-      <c r="H29" s="20" t="s">
-        <v>401</v>
+      <c r="C29" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>236</v>
       </c>
       <c r="I29" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J29" s="20">
+        <v>301</v>
+      </c>
+      <c r="J29" s="14">
         <v>1</v>
       </c>
-      <c r="K29" s="20">
-        <f t="shared" ref="K29" si="11">J29*5</f>
+      <c r="K29" s="14">
+        <f>J29*5</f>
         <v>5</v>
       </c>
       <c r="L29" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M29" s="15">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="N29" s="15">
         <f t="shared" si="2"/>
-        <v>5.25</v>
-      </c>
-      <c r="O29" s="20"/>
-      <c r="P29" s="20"/>
+        <v>4.95</v>
+      </c>
+      <c r="O29" s="14"/>
+      <c r="P29" s="19"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
@@ -3544,46 +3538,46 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C30" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>103</v>
+      <c r="C30" s="22" t="s">
+        <v>386</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="42" t="s">
+        <v>387</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="I30" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="J30" s="14">
-        <v>2</v>
-      </c>
-      <c r="K30" s="14">
-        <f>J30*5</f>
-        <v>10</v>
+        <v>300</v>
+      </c>
+      <c r="G30" s="42" t="s">
+        <v>388</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="I30" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="J30" s="20">
+        <v>1</v>
+      </c>
+      <c r="K30" s="20">
+        <f t="shared" ref="K30" si="11">J30*5</f>
+        <v>5</v>
       </c>
       <c r="L30" s="44" t="s">
-        <v>380</v>
-      </c>
-      <c r="M30" s="48">
-        <v>7.6499999999999999E-2</v>
+        <v>360</v>
+      </c>
+      <c r="M30" s="15">
+        <v>1.05</v>
       </c>
       <c r="N30" s="15">
         <f t="shared" si="2"/>
-        <v>0.76500000000000001</v>
-      </c>
-      <c r="O30" s="14"/>
-      <c r="P30" s="19"/>
+        <v>5.25</v>
+      </c>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
@@ -3594,43 +3588,43 @@
       <c r="C31" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>104</v>
+      <c r="D31" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="H31" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="I31" s="42" t="s">
-        <v>313</v>
-      </c>
-      <c r="J31" s="20">
-        <v>4</v>
-      </c>
-      <c r="K31" s="20">
-        <f t="shared" ref="K31" si="12">J31*5</f>
-        <v>20</v>
+        <v>300</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="I31" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="J31" s="14">
+        <v>2</v>
+      </c>
+      <c r="K31" s="14">
+        <f>J31*5</f>
+        <v>10</v>
       </c>
       <c r="L31" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="M31" s="15" t="s">
-        <v>343</v>
+        <v>368</v>
+      </c>
+      <c r="M31" s="48">
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="N31" s="15">
         <f t="shared" si="2"/>
-        <v>8.2999999999999989</v>
-      </c>
-      <c r="O31" s="20"/>
-      <c r="P31" s="20"/>
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="O31" s="14"/>
+      <c r="P31" s="19"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
@@ -3639,45 +3633,45 @@
         <v>25</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="H32" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="I32" s="41" t="s">
-        <v>312</v>
-      </c>
-      <c r="J32" s="14">
-        <v>1</v>
-      </c>
-      <c r="K32" s="14">
-        <f>J32*5</f>
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I32" s="42" t="s">
+        <v>302</v>
+      </c>
+      <c r="J32" s="20">
+        <v>4</v>
+      </c>
+      <c r="K32" s="20">
+        <f t="shared" ref="K32" si="12">J32*5</f>
+        <v>20</v>
       </c>
       <c r="L32" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M32" s="15" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="N32" s="15">
         <f t="shared" si="2"/>
-        <v>1.75</v>
-      </c>
-      <c r="O32" s="14"/>
-      <c r="P32" s="19"/>
+        <v>8.2999999999999989</v>
+      </c>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
@@ -3685,140 +3679,140 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D33" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>382</v>
+      <c r="D33" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>100</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="G33" s="20" t="s">
-        <v>381</v>
+        <v>147</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>195</v>
       </c>
       <c r="H33" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="I33" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J33" s="20">
+        <v>238</v>
+      </c>
+      <c r="I33" s="41" t="s">
+        <v>301</v>
+      </c>
+      <c r="J33" s="14">
         <v>1</v>
       </c>
-      <c r="K33" s="20">
-        <f t="shared" ref="K33" si="13">J33*5</f>
+      <c r="K33" s="14">
+        <f>J33*5</f>
         <v>5</v>
       </c>
       <c r="L33" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="M33" s="48">
-        <v>0.3</v>
+        <v>360</v>
+      </c>
+      <c r="M33" s="15" t="s">
+        <v>333</v>
       </c>
       <c r="N33" s="15">
         <f t="shared" si="2"/>
-        <v>1.5</v>
-      </c>
-      <c r="O33" s="20"/>
-      <c r="P33" s="20"/>
-    </row>
-    <row r="34" spans="1:16" ht="36" x14ac:dyDescent="0.25">
+        <v>1.75</v>
+      </c>
+      <c r="O33" s="14"/>
+      <c r="P33" s="19"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="16">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C34" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>106</v>
+      <c r="C34" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>370</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>203</v>
+        <v>147</v>
+      </c>
+      <c r="G34" s="20" t="s">
+        <v>369</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="I34" s="41" t="s">
-        <v>312</v>
-      </c>
-      <c r="J34" s="14">
+        <v>238</v>
+      </c>
+      <c r="I34" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="J34" s="20">
         <v>1</v>
       </c>
-      <c r="K34" s="14">
-        <f>J34*5</f>
+      <c r="K34" s="20">
+        <f t="shared" ref="K34" si="13">J34*5</f>
         <v>5</v>
       </c>
       <c r="L34" s="44" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="M34" s="48">
-        <v>0.1661</v>
+        <v>0.3</v>
       </c>
       <c r="N34" s="15">
         <f t="shared" si="2"/>
-        <v>0.83050000000000002</v>
-      </c>
-      <c r="O34" s="14"/>
-      <c r="P34" s="19"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.5</v>
+      </c>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+    </row>
+    <row r="35" spans="1:16" ht="36" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="16">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C35" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="H35" s="20" t="s">
-        <v>248</v>
+      <c r="C35" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>239</v>
       </c>
       <c r="I35" s="41" t="s">
-        <v>312</v>
-      </c>
-      <c r="J35" s="20">
+        <v>301</v>
+      </c>
+      <c r="J35" s="14">
         <v>1</v>
       </c>
-      <c r="K35" s="20">
-        <f t="shared" ref="K35" si="14">J35*5</f>
+      <c r="K35" s="14">
+        <f>J35*5</f>
         <v>5</v>
       </c>
       <c r="L35" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="M35" s="15" t="s">
-        <v>345</v>
+        <v>368</v>
+      </c>
+      <c r="M35" s="48">
+        <v>0.1661</v>
       </c>
       <c r="N35" s="15">
         <f t="shared" si="2"/>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="O35" s="20"/>
-      <c r="P35" s="20"/>
+        <v>0.83050000000000002</v>
+      </c>
+      <c r="O35" s="14"/>
+      <c r="P35" s="19"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
@@ -3829,45 +3823,45 @@
       <c r="C36" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D36" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>249</v>
+      <c r="D36" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>240</v>
       </c>
       <c r="I36" s="41" t="s">
-        <v>312</v>
-      </c>
-      <c r="J36" s="14">
+        <v>301</v>
+      </c>
+      <c r="J36" s="20">
         <v>1</v>
       </c>
-      <c r="K36" s="14">
-        <f>J36*5</f>
+      <c r="K36" s="20">
+        <f t="shared" ref="K36" si="14">J36*5</f>
         <v>5</v>
       </c>
       <c r="L36" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M36" s="15" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="N36" s="15">
         <f t="shared" si="2"/>
-        <v>5.6499999999999995</v>
-      </c>
-      <c r="O36" s="14"/>
-      <c r="P36" s="19"/>
-    </row>
-    <row r="37" spans="1:16" ht="48" x14ac:dyDescent="0.25">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="16">
         <f t="shared" si="0"/>
@@ -3876,90 +3870,90 @@
       <c r="C37" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="G37" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="H37" s="20" t="s">
-        <v>250</v>
+      <c r="D37" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>241</v>
       </c>
       <c r="I37" s="41" t="s">
-        <v>312</v>
-      </c>
-      <c r="J37" s="20">
+        <v>301</v>
+      </c>
+      <c r="J37" s="14">
         <v>1</v>
       </c>
-      <c r="K37" s="20">
-        <f t="shared" ref="K37" si="15">J37*5</f>
+      <c r="K37" s="14">
+        <f>J37*5</f>
         <v>5</v>
       </c>
       <c r="L37" s="44" t="s">
-        <v>380</v>
-      </c>
-      <c r="M37" s="48">
-        <v>3.0800000000000001E-2</v>
+        <v>360</v>
+      </c>
+      <c r="M37" s="15" t="s">
+        <v>335</v>
       </c>
       <c r="N37" s="15">
         <f t="shared" si="2"/>
-        <v>0.154</v>
-      </c>
-      <c r="O37" s="20"/>
-      <c r="P37" s="20"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+        <v>5.6499999999999995</v>
+      </c>
+      <c r="O37" s="14"/>
+      <c r="P37" s="19"/>
+    </row>
+    <row r="38" spans="1:16" ht="48" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="16">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C38" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>239</v>
+      <c r="C38" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>242</v>
       </c>
       <c r="I38" s="41" t="s">
-        <v>283</v>
-      </c>
-      <c r="J38" s="14">
-        <v>3</v>
-      </c>
-      <c r="K38" s="14">
-        <f>J38*5</f>
-        <v>15</v>
+        <v>301</v>
+      </c>
+      <c r="J38" s="20">
+        <v>1</v>
+      </c>
+      <c r="K38" s="20">
+        <f t="shared" ref="K38" si="15">J38*5</f>
+        <v>5</v>
       </c>
       <c r="L38" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="M38" s="15" t="s">
-        <v>347</v>
+        <v>368</v>
+      </c>
+      <c r="M38" s="48">
+        <v>3.0800000000000001E-2</v>
       </c>
       <c r="N38" s="15">
         <f t="shared" si="2"/>
-        <v>0.22499999999999998</v>
-      </c>
-      <c r="O38" s="14"/>
-      <c r="P38" s="19"/>
+        <v>0.154</v>
+      </c>
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
@@ -3967,46 +3961,46 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="H39" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="I39" s="42" t="s">
-        <v>284</v>
-      </c>
-      <c r="J39" s="20">
-        <v>1</v>
-      </c>
-      <c r="K39" s="20">
-        <f t="shared" ref="K39" si="16">J39*5</f>
-        <v>5</v>
+      <c r="D39" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="H39" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="I39" s="41" t="s">
+        <v>274</v>
+      </c>
+      <c r="J39" s="14">
+        <v>3</v>
+      </c>
+      <c r="K39" s="14">
+        <f>J39*5</f>
+        <v>15</v>
       </c>
       <c r="L39" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M39" s="15" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="N39" s="15">
         <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="O39" s="20"/>
-      <c r="P39" s="20"/>
+        <v>0.22499999999999998</v>
+      </c>
+      <c r="O39" s="14"/>
+      <c r="P39" s="19"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
@@ -4014,140 +4008,140 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C40" s="21" t="s">
+      <c r="C40" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="I40" s="41" t="s">
-        <v>285</v>
-      </c>
-      <c r="J40" s="14">
+      <c r="D40" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="I40" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="J40" s="20">
+        <v>1</v>
+      </c>
+      <c r="K40" s="20">
+        <f t="shared" ref="K40" si="16">J40*5</f>
         <v>5</v>
       </c>
-      <c r="K40" s="14">
-        <f>J40*5</f>
-        <v>25</v>
-      </c>
       <c r="L40" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M40" s="15" t="s">
-        <v>348</v>
+        <v>311</v>
       </c>
       <c r="N40" s="15">
         <f t="shared" si="2"/>
-        <v>0.67500000000000004</v>
-      </c>
-      <c r="O40" s="14"/>
-      <c r="P40" s="19"/>
-    </row>
-    <row r="41" spans="1:16" ht="48" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="16">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C41" s="22" t="s">
+      <c r="C41" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D41" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="F41" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="G41" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="H41" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="I41" s="42" t="s">
-        <v>286</v>
-      </c>
-      <c r="J41" s="20">
-        <v>24</v>
-      </c>
-      <c r="K41" s="20">
-        <f t="shared" ref="K41" si="17">J41*5</f>
-        <v>120</v>
+      <c r="D41" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="I41" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="J41" s="14">
+        <v>6</v>
+      </c>
+      <c r="K41" s="14">
+        <f>J41*5</f>
+        <v>30</v>
       </c>
       <c r="L41" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M41" s="15" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="N41" s="15">
         <f t="shared" si="2"/>
-        <v>0.876</v>
-      </c>
-      <c r="O41" s="20"/>
-      <c r="P41" s="20"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.80999999999999994</v>
+      </c>
+      <c r="O41" s="14"/>
+      <c r="P41" s="19"/>
+    </row>
+    <row r="42" spans="1:16" ht="48" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="16">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C42" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="F42" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G42" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="I42" s="41" t="s">
-        <v>287</v>
-      </c>
-      <c r="J42" s="14">
-        <v>1</v>
-      </c>
-      <c r="K42" s="14">
-        <f>J42*5</f>
-        <v>5</v>
+      <c r="C42" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="I42" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="J42" s="20">
+        <v>24</v>
+      </c>
+      <c r="K42" s="20">
+        <f t="shared" ref="K42" si="17">J42*5</f>
+        <v>120</v>
       </c>
       <c r="L42" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M42" s="15" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="N42" s="15">
         <f t="shared" si="2"/>
-        <v>2.9</v>
-      </c>
-      <c r="O42" s="14"/>
-      <c r="P42" s="19"/>
+        <v>0.876</v>
+      </c>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
@@ -4155,93 +4149,93 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C43" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="G43" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="H43" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="I43" s="42" t="s">
-        <v>288</v>
-      </c>
-      <c r="J43" s="20">
+      <c r="C43" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="I43" s="41" t="s">
+        <v>278</v>
+      </c>
+      <c r="J43" s="14">
         <v>1</v>
       </c>
-      <c r="K43" s="20">
-        <f t="shared" ref="K43" si="18">J43*5</f>
+      <c r="K43" s="14">
+        <f>J43*5</f>
         <v>5</v>
       </c>
       <c r="L43" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M43" s="15" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="N43" s="15">
         <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="O43" s="20"/>
-      <c r="P43" s="20"/>
+        <v>2.9</v>
+      </c>
+      <c r="O43" s="14"/>
+      <c r="P43" s="19"/>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="16">
-        <f t="shared" si="0"/>
+        <f>ROW(B44) - ROW($B$7)</f>
         <v>37</v>
       </c>
-      <c r="C44" s="21" t="s">
+      <c r="C44" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D44" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="G44" s="14" t="s">
-        <v>374</v>
+      <c r="D44" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>207</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="I44" s="41" t="s">
-        <v>289</v>
-      </c>
-      <c r="J44" s="14">
-        <v>1</v>
-      </c>
-      <c r="K44" s="14">
-        <f>J44*5</f>
+        <v>231</v>
+      </c>
+      <c r="I44" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="J44" s="20">
         <v>5</v>
       </c>
+      <c r="K44" s="20">
+        <f t="shared" ref="K44" si="18">J44*5</f>
+        <v>25</v>
+      </c>
       <c r="L44" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M44" s="15" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="N44" s="15">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="O44" s="14"/>
-      <c r="P44" s="19"/>
+        <f>M44*K44</f>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
@@ -4253,22 +4247,22 @@
         <v>12</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I45" s="42" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="J45" s="20">
         <v>1</v>
@@ -4278,10 +4272,10 @@
         <v>5</v>
       </c>
       <c r="L45" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M45" s="15" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="N45" s="15">
         <f t="shared" si="2"/>
@@ -4300,22 +4294,22 @@
         <v>12</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I46" s="41" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="J46" s="14">
         <v>1</v>
@@ -4325,10 +4319,10 @@
         <v>5</v>
       </c>
       <c r="L46" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M46" s="15" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="N46" s="15">
         <f t="shared" si="2"/>
@@ -4343,46 +4337,46 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="C47" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="G47" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="H47" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="I47" s="42" t="s">
-        <v>292</v>
-      </c>
-      <c r="J47" s="20">
+      <c r="C47" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="I47" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="J47" s="14">
         <v>4</v>
       </c>
-      <c r="K47" s="20">
-        <f t="shared" ref="K47" si="20">J47*5</f>
+      <c r="K47" s="14">
+        <f>J47*5</f>
         <v>20</v>
       </c>
       <c r="L47" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M47" s="15" t="s">
-        <v>351</v>
+        <v>311</v>
       </c>
       <c r="N47" s="15">
         <f t="shared" si="2"/>
-        <v>0.72</v>
-      </c>
-      <c r="O47" s="20"/>
-      <c r="P47" s="20"/>
+        <v>2</v>
+      </c>
+      <c r="O47" s="14"/>
+      <c r="P47" s="19"/>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
@@ -4390,43 +4384,43 @@
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C48" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F48" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="G48" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="I48" s="41" t="s">
-        <v>293</v>
-      </c>
-      <c r="J48" s="14">
-        <v>4</v>
+      <c r="C48" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="E48" s="42" t="s">
+        <v>391</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="G48" s="42" t="s">
+        <v>392</v>
+      </c>
+      <c r="H48" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="I48" s="42" t="s">
+        <v>393</v>
+      </c>
+      <c r="J48" s="20">
+        <v>1</v>
       </c>
       <c r="K48" s="14">
         <f>J48*5</f>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="L48" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="M48" s="15" t="s">
-        <v>322</v>
+        <v>360</v>
+      </c>
+      <c r="M48" s="15">
+        <v>0.1</v>
       </c>
       <c r="N48" s="15">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="O48" s="14"/>
       <c r="P48" s="19"/>
@@ -4437,187 +4431,187 @@
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C49" s="22" t="s">
-        <v>12</v>
+      <c r="C49" s="21" t="s">
+        <v>13</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="E49" s="42" t="s">
-        <v>403</v>
+        <v>54</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>114</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="G49" s="42" t="s">
-        <v>404</v>
+        <v>152</v>
+      </c>
+      <c r="G49" s="20" t="s">
+        <v>209</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I49" s="42" t="s">
-        <v>405</v>
+        <v>283</v>
       </c>
       <c r="J49" s="20">
         <v>1</v>
       </c>
-      <c r="K49" s="14">
-        <f>J49*5</f>
+      <c r="K49" s="20">
+        <f t="shared" ref="K49" si="20">J49*5</f>
         <v>5</v>
       </c>
       <c r="L49" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="M49" s="15">
-        <v>0.1</v>
+        <v>360</v>
+      </c>
+      <c r="M49" s="15" t="s">
+        <v>367</v>
       </c>
       <c r="N49" s="15">
         <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="O49" s="14"/>
-      <c r="P49" s="19"/>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.50004999999999999</v>
+      </c>
+      <c r="O49" s="20"/>
+      <c r="P49" s="20"/>
+    </row>
+    <row r="50" spans="1:16" ht="36" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="16">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E50" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="F50" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="G50" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="H50" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="I50" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="J50" s="20">
-        <v>1</v>
-      </c>
-      <c r="K50" s="20">
-        <f t="shared" ref="K50" si="21">J50*5</f>
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="G50" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="I50" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="J50" s="14">
+        <v>2</v>
+      </c>
+      <c r="K50" s="14">
+        <f>J50*5</f>
+        <v>10</v>
       </c>
       <c r="L50" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="M50" s="15" t="s">
-        <v>379</v>
+        <v>368</v>
+      </c>
+      <c r="M50" s="48">
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="N50" s="15">
         <f t="shared" si="2"/>
-        <v>0.50004999999999999</v>
-      </c>
-      <c r="O50" s="20"/>
-      <c r="P50" s="20"/>
-    </row>
-    <row r="51" spans="1:16" ht="36" x14ac:dyDescent="0.25">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="O50" s="14"/>
+      <c r="P50" s="19"/>
+    </row>
+    <row r="51" spans="1:16" ht="24" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="16">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="C51" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E51" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="F51" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="G51" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="H51" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="I51" s="41" t="s">
-        <v>295</v>
-      </c>
-      <c r="J51" s="14">
-        <v>2</v>
-      </c>
-      <c r="K51" s="14">
-        <f>J51*5</f>
-        <v>10</v>
+      <c r="D51" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="F51" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="G51" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="H51" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="I51" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="J51" s="20">
+        <v>3</v>
+      </c>
+      <c r="K51" s="20">
+        <f t="shared" ref="K51" si="21">J51*5</f>
+        <v>15</v>
       </c>
       <c r="L51" s="44" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="M51" s="48">
-        <v>8.9999999999999998E-4</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="N51" s="15">
         <f t="shared" si="2"/>
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="O51" s="14"/>
-      <c r="P51" s="19"/>
-    </row>
-    <row r="52" spans="1:16" ht="24" x14ac:dyDescent="0.25">
+        <v>6.3E-2</v>
+      </c>
+      <c r="O51" s="20"/>
+      <c r="P51" s="20"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="16">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C52" s="22" t="s">
+      <c r="C52" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D52" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E52" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="F52" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="G52" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="H52" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="I52" s="42" t="s">
-        <v>296</v>
-      </c>
-      <c r="J52" s="20">
-        <v>3</v>
-      </c>
-      <c r="K52" s="20">
-        <f t="shared" ref="K52" si="22">J52*5</f>
-        <v>15</v>
+      <c r="D52" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="H52" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="I52" s="41" t="s">
+        <v>286</v>
+      </c>
+      <c r="J52" s="14">
+        <v>2</v>
+      </c>
+      <c r="K52" s="14">
+        <f>J52*5</f>
+        <v>10</v>
       </c>
       <c r="L52" s="44" t="s">
-        <v>380</v>
-      </c>
-      <c r="M52" s="48">
-        <v>4.1999999999999997E-3</v>
+        <v>360</v>
+      </c>
+      <c r="M52" s="15" t="s">
+        <v>341</v>
       </c>
       <c r="N52" s="15">
         <f t="shared" si="2"/>
-        <v>6.3E-2</v>
-      </c>
-      <c r="O52" s="20"/>
-      <c r="P52" s="20"/>
+        <v>1.2</v>
+      </c>
+      <c r="O52" s="14"/>
+      <c r="P52" s="19"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
@@ -4625,46 +4619,46 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C53" s="21" t="s">
+      <c r="C53" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D53" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="F53" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="G53" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="H53" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="I53" s="41" t="s">
-        <v>297</v>
-      </c>
-      <c r="J53" s="14">
+      <c r="D53" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F53" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="G53" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="H53" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I53" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="J53" s="20">
         <v>2</v>
       </c>
-      <c r="K53" s="14">
-        <f>J53*5</f>
+      <c r="K53" s="20">
+        <f t="shared" ref="K53" si="22">J53*5</f>
         <v>10</v>
       </c>
       <c r="L53" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M53" s="15" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="N53" s="15">
         <f t="shared" si="2"/>
-        <v>1.2</v>
-      </c>
-      <c r="O53" s="14"/>
-      <c r="P53" s="19"/>
+        <v>0.86749999999999994</v>
+      </c>
+      <c r="O53" s="20"/>
+      <c r="P53" s="20"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
@@ -4672,46 +4666,46 @@
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C54" s="22" t="s">
+      <c r="C54" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D54" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="E54" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="F54" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="G54" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="H54" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="I54" s="42" t="s">
-        <v>298</v>
-      </c>
-      <c r="J54" s="20">
-        <v>2</v>
-      </c>
-      <c r="K54" s="20">
-        <f t="shared" ref="K54" si="23">J54*5</f>
-        <v>10</v>
+      <c r="D54" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="H54" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="I54" s="41" t="s">
+        <v>288</v>
+      </c>
+      <c r="J54" s="14">
+        <v>1</v>
+      </c>
+      <c r="K54" s="14">
+        <f>J54*5</f>
+        <v>5</v>
       </c>
       <c r="L54" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M54" s="15" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="N54" s="15">
         <f t="shared" si="2"/>
-        <v>0.86749999999999994</v>
-      </c>
-      <c r="O54" s="20"/>
-      <c r="P54" s="20"/>
+        <v>0.43374999999999997</v>
+      </c>
+      <c r="O54" s="14"/>
+      <c r="P54" s="19"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
@@ -4719,46 +4713,46 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C55" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E55" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="F55" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="G55" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="H55" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="I55" s="41" t="s">
-        <v>299</v>
-      </c>
-      <c r="J55" s="14">
+      <c r="C55" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="G55" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="H55" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="I55" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="J55" s="20">
         <v>1</v>
       </c>
-      <c r="K55" s="14">
-        <f>J55*5</f>
+      <c r="K55" s="20">
+        <f t="shared" ref="K55" si="23">J55*5</f>
         <v>5</v>
       </c>
       <c r="L55" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M55" s="15" t="s">
-        <v>353</v>
+        <v>317</v>
       </c>
       <c r="N55" s="15">
         <f t="shared" si="2"/>
-        <v>0.43374999999999997</v>
-      </c>
-      <c r="O55" s="14"/>
-      <c r="P55" s="19"/>
+        <v>1.45</v>
+      </c>
+      <c r="O55" s="20"/>
+      <c r="P55" s="20"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
@@ -4766,140 +4760,140 @@
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C56" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E56" s="20" t="s">
-        <v>127</v>
+      <c r="C56" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>120</v>
       </c>
       <c r="F56" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="G56" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="H56" s="20" t="s">
-        <v>256</v>
+        <v>300</v>
+      </c>
+      <c r="G56" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="H56" s="14" t="s">
+        <v>248</v>
       </c>
       <c r="I56" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J56" s="20">
-        <v>1</v>
-      </c>
-      <c r="K56" s="20">
-        <f t="shared" ref="K56" si="24">J56*5</f>
-        <v>5</v>
+        <v>301</v>
+      </c>
+      <c r="J56" s="14">
+        <v>2</v>
+      </c>
+      <c r="K56" s="14">
+        <f>J56*5</f>
+        <v>10</v>
       </c>
       <c r="L56" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M56" s="15" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="N56" s="15">
         <f t="shared" si="2"/>
-        <v>1.45</v>
-      </c>
-      <c r="O56" s="20"/>
-      <c r="P56" s="20"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+        <v>9.83</v>
+      </c>
+      <c r="O56" s="14"/>
+      <c r="P56" s="19"/>
+    </row>
+    <row r="57" spans="1:16" ht="36" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="16">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C57" s="21" t="s">
+      <c r="C57" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D57" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E57" s="14" t="s">
-        <v>127</v>
+      <c r="D57" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>121</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="G57" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="H57" s="14" t="s">
-        <v>257</v>
+        <v>300</v>
+      </c>
+      <c r="G57" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="H57" s="20" t="s">
+        <v>249</v>
       </c>
       <c r="I57" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J57" s="14">
-        <v>2</v>
-      </c>
-      <c r="K57" s="14">
-        <f>J57*5</f>
-        <v>10</v>
+        <v>301</v>
+      </c>
+      <c r="J57" s="20">
+        <v>3</v>
+      </c>
+      <c r="K57" s="20">
+        <f t="shared" ref="K57" si="24">J57*5</f>
+        <v>15</v>
       </c>
       <c r="L57" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="M57" s="15" t="s">
-        <v>354</v>
+        <v>368</v>
+      </c>
+      <c r="M57" s="48">
+        <v>0.36980000000000002</v>
       </c>
       <c r="N57" s="15">
         <f t="shared" si="2"/>
-        <v>9.83</v>
-      </c>
-      <c r="O57" s="14"/>
-      <c r="P57" s="19"/>
-    </row>
-    <row r="58" spans="1:16" ht="36" x14ac:dyDescent="0.25">
+        <v>5.5470000000000006</v>
+      </c>
+      <c r="O57" s="20"/>
+      <c r="P57" s="20"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="16">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C58" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D58" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E58" s="20" t="s">
-        <v>128</v>
+      <c r="C58" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="F58" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="G58" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="H58" s="20" t="s">
-        <v>258</v>
+        <v>300</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="H58" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="I58" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J58" s="20">
-        <v>3</v>
-      </c>
-      <c r="K58" s="20">
-        <f t="shared" ref="K58" si="25">J58*5</f>
-        <v>15</v>
+        <v>301</v>
+      </c>
+      <c r="J58" s="14">
+        <v>1</v>
+      </c>
+      <c r="K58" s="14">
+        <f>J58*5</f>
+        <v>5</v>
       </c>
       <c r="L58" s="44" t="s">
-        <v>380</v>
-      </c>
-      <c r="M58" s="48">
-        <v>0.36980000000000002</v>
+        <v>360</v>
+      </c>
+      <c r="M58" s="15" t="s">
+        <v>344</v>
       </c>
       <c r="N58" s="15">
         <f t="shared" si="2"/>
-        <v>5.5470000000000006</v>
-      </c>
-      <c r="O58" s="20"/>
-      <c r="P58" s="20"/>
+        <v>8.35</v>
+      </c>
+      <c r="O58" s="14"/>
+      <c r="P58" s="19"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
@@ -4907,46 +4901,46 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C59" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>129</v>
+      <c r="C59" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>123</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="G59" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="H59" s="14" t="s">
-        <v>259</v>
+        <v>160</v>
+      </c>
+      <c r="G59" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="H59" s="20" t="s">
+        <v>251</v>
       </c>
       <c r="I59" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J59" s="14">
+        <v>301</v>
+      </c>
+      <c r="J59" s="20">
         <v>1</v>
       </c>
-      <c r="K59" s="14">
-        <f>J59*5</f>
+      <c r="K59" s="20">
+        <f t="shared" ref="K59" si="25">J59*5</f>
         <v>5</v>
       </c>
       <c r="L59" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M59" s="15" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="N59" s="15">
         <f t="shared" si="2"/>
-        <v>8.35</v>
-      </c>
-      <c r="O59" s="14"/>
-      <c r="P59" s="19"/>
+        <v>6.75</v>
+      </c>
+      <c r="O59" s="20"/>
+      <c r="P59" s="20"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
@@ -4954,46 +4948,46 @@
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C60" s="22" t="s">
+      <c r="C60" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E60" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="F60" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="G60" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="H60" s="20" t="s">
-        <v>260</v>
+      <c r="D60" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F60" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G60" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="H60" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="I60" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J60" s="20">
+        <v>301</v>
+      </c>
+      <c r="J60" s="14">
         <v>1</v>
       </c>
-      <c r="K60" s="20">
-        <f t="shared" ref="K60" si="26">J60*5</f>
+      <c r="K60" s="14">
+        <f>J60*5</f>
         <v>5</v>
       </c>
       <c r="L60" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M60" s="15" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="N60" s="15">
         <f t="shared" si="2"/>
-        <v>6.75</v>
-      </c>
-      <c r="O60" s="20"/>
-      <c r="P60" s="20"/>
+        <v>15.25</v>
+      </c>
+      <c r="O60" s="14"/>
+      <c r="P60" s="19"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
@@ -5001,46 +4995,46 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C61" s="21" t="s">
+      <c r="C61" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D61" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E61" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="F61" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="G61" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="H61" s="14" t="s">
-        <v>261</v>
+      <c r="D61" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G61" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>251</v>
       </c>
       <c r="I61" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J61" s="14">
+        <v>301</v>
+      </c>
+      <c r="J61" s="20">
         <v>1</v>
       </c>
-      <c r="K61" s="14">
-        <f>J61*5</f>
+      <c r="K61" s="20">
+        <f t="shared" ref="K61" si="26">J61*5</f>
         <v>5</v>
       </c>
       <c r="L61" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M61" s="15" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="N61" s="15">
         <f t="shared" si="2"/>
-        <v>15.25</v>
-      </c>
-      <c r="O61" s="14"/>
-      <c r="P61" s="19"/>
+        <v>10.9</v>
+      </c>
+      <c r="O61" s="20"/>
+      <c r="P61" s="20"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
@@ -5048,46 +5042,46 @@
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="C62" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D62" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E62" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="F62" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="G62" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="H62" s="20" t="s">
-        <v>260</v>
+      <c r="D62" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E62" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="F62" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="G62" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="I62" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J62" s="20">
+        <v>301</v>
+      </c>
+      <c r="J62" s="14">
         <v>1</v>
       </c>
-      <c r="K62" s="20">
-        <f t="shared" ref="K62" si="27">J62*5</f>
+      <c r="K62" s="14">
+        <f>J62*5</f>
         <v>5</v>
       </c>
       <c r="L62" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M62" s="15" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="N62" s="15">
         <f t="shared" si="2"/>
-        <v>10.9</v>
-      </c>
-      <c r="O62" s="20"/>
-      <c r="P62" s="20"/>
+        <v>13.700000000000001</v>
+      </c>
+      <c r="O62" s="14"/>
+      <c r="P62" s="19"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
@@ -5098,45 +5092,45 @@
       <c r="C63" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E63" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="F63" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="G63" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="H63" s="14" t="s">
-        <v>260</v>
+      <c r="D63" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="F63" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G63" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="H63" s="20" t="s">
+        <v>251</v>
       </c>
       <c r="I63" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J63" s="14">
+        <v>301</v>
+      </c>
+      <c r="J63" s="20">
         <v>1</v>
       </c>
-      <c r="K63" s="14">
-        <f>J63*5</f>
+      <c r="K63" s="20">
+        <f t="shared" ref="K63" si="27">J63*5</f>
         <v>5</v>
       </c>
       <c r="L63" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M63" s="15" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="N63" s="15">
         <f t="shared" si="2"/>
-        <v>13.700000000000001</v>
-      </c>
-      <c r="O63" s="14"/>
-      <c r="P63" s="19"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+        <v>6.05</v>
+      </c>
+      <c r="O63" s="20"/>
+      <c r="P63" s="20"/>
+    </row>
+    <row r="64" spans="1:16" ht="24" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="16">
         <f t="shared" si="0"/>
@@ -5145,90 +5139,90 @@
       <c r="C64" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D64" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E64" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F64" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="G64" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="H64" s="20" t="s">
-        <v>260</v>
+      <c r="D64" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="F64" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="G64" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="H64" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="I64" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J64" s="20">
+        <v>301</v>
+      </c>
+      <c r="J64" s="14">
         <v>1</v>
       </c>
-      <c r="K64" s="20">
-        <f t="shared" ref="K64" si="28">J64*5</f>
+      <c r="K64" s="14">
+        <f>J64*5</f>
         <v>5</v>
       </c>
       <c r="L64" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M64" s="15" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="N64" s="15">
         <f t="shared" si="2"/>
-        <v>6.05</v>
-      </c>
-      <c r="O64" s="20"/>
-      <c r="P64" s="20"/>
-    </row>
-    <row r="65" spans="1:16" ht="24" x14ac:dyDescent="0.25">
+        <v>3.05</v>
+      </c>
+      <c r="O64" s="14"/>
+      <c r="P64" s="19"/>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="16">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C65" s="21" t="s">
+      <c r="C65" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D65" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E65" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="F65" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="G65" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="H65" s="14" t="s">
-        <v>262</v>
+      <c r="D65" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="F65" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="G65" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="H65" s="20" t="s">
+        <v>254</v>
       </c>
       <c r="I65" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J65" s="14">
+        <v>301</v>
+      </c>
+      <c r="J65" s="20">
         <v>1</v>
       </c>
-      <c r="K65" s="14">
-        <f>J65*5</f>
+      <c r="K65" s="20">
+        <f t="shared" ref="K65" si="28">J65*5</f>
         <v>5</v>
       </c>
       <c r="L65" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M65" s="15" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="N65" s="15">
         <f t="shared" si="2"/>
-        <v>3.05</v>
-      </c>
-      <c r="O65" s="14"/>
-      <c r="P65" s="19"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="O65" s="20"/>
+      <c r="P65" s="20"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
@@ -5236,46 +5230,46 @@
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="C66" s="22" t="s">
+      <c r="C66" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D66" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E66" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="F66" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="G66" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="H66" s="20" t="s">
-        <v>263</v>
+      <c r="D66" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E66" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="F66" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G66" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="H66" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="I66" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J66" s="20">
+        <v>301</v>
+      </c>
+      <c r="J66" s="14">
         <v>1</v>
       </c>
-      <c r="K66" s="20">
-        <f t="shared" ref="K66" si="29">J66*5</f>
+      <c r="K66" s="14">
+        <f>J66*5</f>
         <v>5</v>
       </c>
       <c r="L66" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M66" s="15" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="N66" s="15">
         <f t="shared" si="2"/>
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="O66" s="20"/>
-      <c r="P66" s="20"/>
+        <v>2</v>
+      </c>
+      <c r="O66" s="14"/>
+      <c r="P66" s="19"/>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
@@ -5283,140 +5277,140 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C67" s="21" t="s">
+      <c r="C67" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D67" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E67" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="F67" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="G67" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="H67" s="14" t="s">
-        <v>263</v>
+      <c r="D67" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="F67" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G67" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="H67" s="20" t="s">
+        <v>251</v>
       </c>
       <c r="I67" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J67" s="14">
+        <v>301</v>
+      </c>
+      <c r="J67" s="20">
         <v>1</v>
       </c>
-      <c r="K67" s="14">
-        <f>J67*5</f>
+      <c r="K67" s="20">
+        <f t="shared" ref="K67" si="29">J67*5</f>
         <v>5</v>
       </c>
       <c r="L67" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M67" s="15" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="N67" s="15">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="O67" s="14"/>
-      <c r="P67" s="19"/>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+        <v>31.05</v>
+      </c>
+      <c r="O67" s="20"/>
+      <c r="P67" s="20"/>
+    </row>
+    <row r="68" spans="1:16" ht="36" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="16">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="C68" s="22" t="s">
+      <c r="C68" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E68" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="F68" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="G68" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="H68" s="20" t="s">
-        <v>260</v>
+      <c r="D68" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E68" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="F68" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="G68" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="H68" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="I68" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J68" s="20">
+        <v>301</v>
+      </c>
+      <c r="J68" s="14">
         <v>1</v>
       </c>
-      <c r="K68" s="20">
-        <f t="shared" ref="K68" si="30">J68*5</f>
+      <c r="K68" s="14">
+        <f>J68*5</f>
         <v>5</v>
       </c>
       <c r="L68" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M68" s="15" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="N68" s="15">
         <f t="shared" si="2"/>
-        <v>31.05</v>
-      </c>
-      <c r="O68" s="20"/>
-      <c r="P68" s="20"/>
-    </row>
-    <row r="69" spans="1:16" ht="36" x14ac:dyDescent="0.25">
+        <v>189.94565</v>
+      </c>
+      <c r="O68" s="14"/>
+      <c r="P68" s="19"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="16">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C69" s="21" t="s">
+      <c r="C69" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D69" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="E69" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="F69" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="G69" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="H69" s="14" t="s">
-        <v>260</v>
+      <c r="D69" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F69" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="G69" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="H69" s="20" t="s">
+        <v>255</v>
       </c>
       <c r="I69" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J69" s="14">
+        <v>301</v>
+      </c>
+      <c r="J69" s="20">
         <v>1</v>
       </c>
-      <c r="K69" s="14">
-        <f>J69*5</f>
+      <c r="K69" s="20">
+        <f t="shared" ref="K69" si="30">J69*5</f>
         <v>5</v>
       </c>
       <c r="L69" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M69" s="15" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="N69" s="15">
         <f t="shared" si="2"/>
-        <v>189.94565</v>
-      </c>
-      <c r="O69" s="14"/>
-      <c r="P69" s="19"/>
+        <v>5.6000000000000005</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20"/>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
@@ -5424,46 +5418,46 @@
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C70" s="22" t="s">
+      <c r="C70" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D70" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="E70" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="F70" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="G70" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="H70" s="20" t="s">
-        <v>264</v>
+      <c r="D70" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E70" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F70" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="G70" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="H70" s="14" t="s">
+        <v>256</v>
       </c>
       <c r="I70" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J70" s="20">
+        <v>301</v>
+      </c>
+      <c r="J70" s="14">
         <v>1</v>
       </c>
-      <c r="K70" s="20">
-        <f t="shared" ref="K70" si="31">J70*5</f>
+      <c r="K70" s="14">
+        <f>J70*5</f>
         <v>5</v>
       </c>
       <c r="L70" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M70" s="15" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="N70" s="15">
         <f t="shared" si="2"/>
-        <v>5.6000000000000005</v>
-      </c>
-      <c r="O70" s="20"/>
-      <c r="P70" s="20"/>
+        <v>30.950000000000003</v>
+      </c>
+      <c r="O70" s="14"/>
+      <c r="P70" s="19"/>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
@@ -5471,373 +5465,349 @@
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C71" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="E71" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="F71" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="G71" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="H71" s="14" t="s">
-        <v>265</v>
+      <c r="C71" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="F71" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G71" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="H71" s="20" t="s">
+        <v>240</v>
       </c>
       <c r="I71" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J71" s="14">
+        <v>289</v>
+      </c>
+      <c r="J71" s="20">
         <v>1</v>
       </c>
-      <c r="K71" s="14">
-        <f>J71*5</f>
+      <c r="K71" s="20">
+        <f t="shared" ref="K71" si="31">J71*5</f>
         <v>5</v>
       </c>
       <c r="L71" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M71" s="15" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="N71" s="15">
         <f t="shared" si="2"/>
-        <v>30.950000000000003</v>
-      </c>
-      <c r="O71" s="14"/>
-      <c r="P71" s="19"/>
+        <v>3.8</v>
+      </c>
+      <c r="O71" s="20"/>
+      <c r="P71" s="20"/>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B72:B77" si="32">ROW(B72) - ROW($B$7)</f>
         <v>65</v>
       </c>
-      <c r="C72" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D72" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E72" s="20" t="s">
-        <v>141</v>
+      <c r="C72" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>135</v>
       </c>
       <c r="F72" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="G72" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="H72" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="I72" s="42" t="s">
         <v>300</v>
       </c>
-      <c r="J72" s="20">
+      <c r="G72" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="H72" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="I72" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="J72" s="14">
         <v>1</v>
       </c>
-      <c r="K72" s="20">
-        <f t="shared" ref="K72" si="32">J72*5</f>
+      <c r="K72" s="14">
+        <f>J72*5</f>
         <v>5</v>
       </c>
       <c r="L72" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="M72" s="15" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="N72" s="15">
         <f t="shared" si="2"/>
-        <v>3.8</v>
-      </c>
-      <c r="O72" s="20"/>
-      <c r="P72" s="20"/>
+        <v>2.3000000000000003</v>
+      </c>
+      <c r="O72" s="14"/>
+      <c r="P72" s="19"/>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="16">
-        <f t="shared" ref="B73:B78" si="33">ROW(B73) - ROW($B$7)</f>
+        <f t="shared" si="32"/>
         <v>66</v>
       </c>
-      <c r="C73" s="21" t="s">
+      <c r="C73" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D73" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E73" s="14" t="s">
-        <v>142</v>
+      <c r="D73" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>136</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="G73" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="H73" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="I73" s="41" t="s">
-        <v>301</v>
-      </c>
-      <c r="J73" s="14">
+        <v>173</v>
+      </c>
+      <c r="G73" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="H73" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="I73" s="42" t="s">
+        <v>291</v>
+      </c>
+      <c r="J73" s="20">
         <v>1</v>
       </c>
-      <c r="K73" s="14">
-        <f>J73*5</f>
+      <c r="K73" s="20">
+        <f t="shared" ref="K73:K77" si="33">J73*5</f>
         <v>5</v>
       </c>
-      <c r="L73" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="M73" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="N73" s="15">
+      <c r="L73" s="50" t="s">
+        <v>360</v>
+      </c>
+      <c r="M73" s="62" t="s">
+        <v>359</v>
+      </c>
+      <c r="N73" s="62">
         <f t="shared" si="2"/>
-        <v>2.3000000000000003</v>
-      </c>
-      <c r="O73" s="14"/>
-      <c r="P73" s="19"/>
+        <v>3.15</v>
+      </c>
+      <c r="O73" s="20"/>
+      <c r="P73" s="20"/>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="16">
+        <f t="shared" si="32"/>
+        <v>67</v>
+      </c>
+      <c r="C74" s="66" t="s">
+        <v>375</v>
+      </c>
+      <c r="D74" s="67" t="s">
+        <v>301</v>
+      </c>
+      <c r="E74" s="68" t="s">
+        <v>394</v>
+      </c>
+      <c r="F74" s="67" t="s">
+        <v>300</v>
+      </c>
+      <c r="G74" s="68" t="s">
+        <v>395</v>
+      </c>
+      <c r="H74" s="67" t="s">
+        <v>396</v>
+      </c>
+      <c r="I74" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="J74" s="67">
+        <v>1</v>
+      </c>
+      <c r="K74" s="67">
         <f t="shared" si="33"/>
-        <v>67</v>
-      </c>
-      <c r="C74" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D74" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E74" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="F74" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="G74" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="H74" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="I74" s="42" t="s">
-        <v>302</v>
-      </c>
-      <c r="J74" s="20">
-        <v>1</v>
-      </c>
-      <c r="K74" s="20">
-        <f t="shared" ref="K74:K78" si="34">J74*5</f>
         <v>5</v>
       </c>
-      <c r="L74" s="50" t="s">
-        <v>371</v>
-      </c>
-      <c r="M74" s="62" t="s">
-        <v>370</v>
-      </c>
-      <c r="N74" s="62">
+      <c r="L74" s="69" t="s">
+        <v>360</v>
+      </c>
+      <c r="M74" s="58">
+        <v>2.31</v>
+      </c>
+      <c r="N74" s="70">
         <f t="shared" si="2"/>
-        <v>3.15</v>
-      </c>
-      <c r="O74" s="20"/>
-      <c r="P74" s="20"/>
+        <v>11.55</v>
+      </c>
+      <c r="O74" s="67"/>
+      <c r="P74" s="67"/>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>68</v>
       </c>
       <c r="C75" s="66" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="D75" s="67" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="E75" s="68" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="F75" s="67" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="G75" s="68" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="H75" s="67" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="I75" s="68" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="J75" s="67">
         <v>1</v>
       </c>
       <c r="K75" s="67">
-        <f t="shared" si="34"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L75" s="69" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="M75" s="58">
-        <v>2.31</v>
+        <v>60</v>
       </c>
       <c r="N75" s="70">
         <f t="shared" si="2"/>
-        <v>11.55</v>
+        <v>60</v>
       </c>
       <c r="O75" s="67"/>
       <c r="P75" s="67"/>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" ht="36" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="16">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>69</v>
       </c>
-      <c r="C76" s="66" t="s">
-        <v>387</v>
-      </c>
-      <c r="D76" s="67" t="s">
-        <v>312</v>
-      </c>
-      <c r="E76" s="68" t="s">
-        <v>409</v>
+      <c r="C76" s="52" t="s">
+        <v>375</v>
+      </c>
+      <c r="D76" s="59" t="s">
+        <v>301</v>
+      </c>
+      <c r="E76" s="72" t="s">
+        <v>400</v>
       </c>
       <c r="F76" s="67" t="s">
-        <v>311</v>
-      </c>
-      <c r="G76" s="68" t="s">
-        <v>410</v>
-      </c>
-      <c r="H76" s="67" t="s">
-        <v>411</v>
-      </c>
-      <c r="I76" s="68" t="s">
-        <v>312</v>
-      </c>
-      <c r="J76" s="67">
+        <v>300</v>
+      </c>
+      <c r="G76" s="72" t="s">
+        <v>401</v>
+      </c>
+      <c r="H76" s="59" t="s">
+        <v>402</v>
+      </c>
+      <c r="I76" s="72" t="s">
+        <v>301</v>
+      </c>
+      <c r="J76" s="59">
         <v>1</v>
       </c>
       <c r="K76" s="67">
         <v>1</v>
       </c>
       <c r="L76" s="69" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="M76" s="58">
-        <v>60</v>
+        <v>5.59</v>
       </c>
       <c r="N76" s="70">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>5.59</v>
       </c>
       <c r="O76" s="67"/>
       <c r="P76" s="67"/>
     </row>
-    <row r="77" spans="1:16" ht="36" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="16">
+        <f t="shared" si="32"/>
+        <v>70</v>
+      </c>
+      <c r="C77" s="63" t="s">
+        <v>375</v>
+      </c>
+      <c r="D77" s="61" t="s">
+        <v>301</v>
+      </c>
+      <c r="E77" s="64" t="s">
+        <v>376</v>
+      </c>
+      <c r="F77" s="61" t="s">
+        <v>301</v>
+      </c>
+      <c r="G77" s="64" t="s">
+        <v>377</v>
+      </c>
+      <c r="H77" s="61" t="s">
+        <v>301</v>
+      </c>
+      <c r="I77" s="64" t="s">
+        <v>301</v>
+      </c>
+      <c r="J77" s="61">
+        <v>1</v>
+      </c>
+      <c r="K77" s="61">
         <f t="shared" si="33"/>
-        <v>70</v>
-      </c>
-      <c r="C77" s="52" t="s">
-        <v>387</v>
-      </c>
-      <c r="D77" s="59" t="s">
-        <v>312</v>
-      </c>
-      <c r="E77" s="79" t="s">
-        <v>412</v>
-      </c>
-      <c r="F77" s="67" t="s">
-        <v>311</v>
-      </c>
-      <c r="G77" s="79" t="s">
-        <v>413</v>
-      </c>
-      <c r="H77" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="I77" s="79" t="s">
-        <v>312</v>
-      </c>
-      <c r="J77" s="59">
-        <v>1</v>
-      </c>
-      <c r="K77" s="67">
-        <v>1</v>
-      </c>
-      <c r="L77" s="69" t="s">
-        <v>414</v>
-      </c>
-      <c r="M77" s="58">
-        <v>5.59</v>
-      </c>
-      <c r="N77" s="70">
-        <f t="shared" si="2"/>
-        <v>5.59</v>
+        <v>5</v>
+      </c>
+      <c r="L77" s="65" t="s">
+        <v>378</v>
+      </c>
+      <c r="M77" s="60">
+        <v>6.8</v>
+      </c>
+      <c r="N77" s="71">
+        <f t="shared" ref="N77" si="34">M77*K77</f>
+        <v>34</v>
       </c>
       <c r="O77" s="67"/>
       <c r="P77" s="67"/>
     </row>
-    <row r="78" spans="1:16" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
-      <c r="B78" s="16">
-        <f t="shared" si="33"/>
-        <v>71</v>
-      </c>
-      <c r="C78" s="63" t="s">
-        <v>387</v>
-      </c>
-      <c r="D78" s="61" t="s">
-        <v>312</v>
-      </c>
-      <c r="E78" s="64" t="s">
-        <v>388</v>
-      </c>
-      <c r="F78" s="61" t="s">
-        <v>312</v>
-      </c>
-      <c r="G78" s="64" t="s">
-        <v>389</v>
-      </c>
-      <c r="H78" s="61" t="s">
-        <v>312</v>
-      </c>
-      <c r="I78" s="64" t="s">
-        <v>312</v>
-      </c>
-      <c r="J78" s="61">
-        <v>1</v>
-      </c>
-      <c r="K78" s="61">
-        <f t="shared" si="34"/>
-        <v>5</v>
-      </c>
-      <c r="L78" s="65" t="s">
-        <v>390</v>
-      </c>
-      <c r="M78" s="60">
-        <v>6.8</v>
-      </c>
-      <c r="N78" s="71">
-        <f t="shared" ref="N78" si="35">M78*K78</f>
-        <v>34</v>
-      </c>
-      <c r="O78" s="67"/>
-      <c r="P78" s="67"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="75" t="s">
+        <v>365</v>
+      </c>
+      <c r="M78" s="76"/>
+      <c r="N78" s="49">
+        <f>SUM(N8:N77)</f>
+        <v>601.28645000000006</v>
+      </c>
+      <c r="O78" s="1"/>
+      <c r="P78" s="1"/>
     </row>
     <row r="79" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
@@ -5851,48 +5821,25 @@
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
-      <c r="L79" s="74" t="s">
-        <v>377</v>
-      </c>
-      <c r="M79" s="75"/>
-      <c r="N79" s="49">
-        <f>SUM(N8:N78)</f>
-        <v>601.93745000000001</v>
+      <c r="L79" s="75" t="s">
+        <v>366</v>
+      </c>
+      <c r="M79" s="76"/>
+      <c r="N79" s="18">
+        <f>N78/5</f>
+        <v>120.25729000000001</v>
       </c>
       <c r="O79" s="1"/>
       <c r="P79" s="1"/>
     </row>
-    <row r="80" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
-      <c r="K80" s="1"/>
-      <c r="L80" s="74" t="s">
-        <v>378</v>
-      </c>
-      <c r="M80" s="75"/>
-      <c r="N80" s="18">
-        <f>N79/5</f>
-        <v>120.38749</v>
-      </c>
-      <c r="O80" s="1"/>
-      <c r="P80" s="1"/>
-    </row>
-    <row r="92" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K92" s="36"/>
+    <row r="91" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K91" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="I1:P1"/>
+    <mergeCell ref="L78:M78"/>
     <mergeCell ref="L79:M79"/>
-    <mergeCell ref="L80:M80"/>
     <mergeCell ref="P2:P6"/>
   </mergeCells>
   <hyperlinks>
@@ -5911,72 +5858,71 @@
     <hyperlink ref="L20" r:id="rId13"/>
     <hyperlink ref="L21" r:id="rId14"/>
     <hyperlink ref="L23" r:id="rId15"/>
-    <hyperlink ref="L24" r:id="rId16"/>
-    <hyperlink ref="L25" r:id="rId17"/>
-    <hyperlink ref="L31" r:id="rId18"/>
-    <hyperlink ref="L32" r:id="rId19"/>
-    <hyperlink ref="L35" r:id="rId20"/>
-    <hyperlink ref="L36" r:id="rId21"/>
-    <hyperlink ref="L38" r:id="rId22"/>
-    <hyperlink ref="L39" r:id="rId23"/>
-    <hyperlink ref="L40" r:id="rId24"/>
-    <hyperlink ref="L41" r:id="rId25"/>
-    <hyperlink ref="L42" r:id="rId26"/>
-    <hyperlink ref="L43" r:id="rId27"/>
-    <hyperlink ref="L44" r:id="rId28"/>
-    <hyperlink ref="L45" r:id="rId29"/>
-    <hyperlink ref="L46" r:id="rId30"/>
-    <hyperlink ref="L47" r:id="rId31"/>
-    <hyperlink ref="L48" r:id="rId32"/>
-    <hyperlink ref="L50" r:id="rId33"/>
-    <hyperlink ref="L55" r:id="rId34"/>
-    <hyperlink ref="L54" r:id="rId35"/>
-    <hyperlink ref="L53" r:id="rId36"/>
-    <hyperlink ref="L56" r:id="rId37"/>
-    <hyperlink ref="L57" r:id="rId38"/>
-    <hyperlink ref="L59" r:id="rId39"/>
-    <hyperlink ref="L60" r:id="rId40"/>
-    <hyperlink ref="L61" r:id="rId41"/>
-    <hyperlink ref="L62" r:id="rId42"/>
-    <hyperlink ref="L63" r:id="rId43"/>
-    <hyperlink ref="L64" r:id="rId44"/>
-    <hyperlink ref="L65" r:id="rId45"/>
-    <hyperlink ref="L66" r:id="rId46"/>
-    <hyperlink ref="L67" r:id="rId47"/>
-    <hyperlink ref="L68" r:id="rId48"/>
-    <hyperlink ref="L69" r:id="rId49"/>
-    <hyperlink ref="L70" r:id="rId50"/>
-    <hyperlink ref="L71" r:id="rId51"/>
-    <hyperlink ref="L72" r:id="rId52"/>
-    <hyperlink ref="L73" r:id="rId53"/>
-    <hyperlink ref="L74" r:id="rId54"/>
-    <hyperlink ref="L27" r:id="rId55"/>
-    <hyperlink ref="L33" r:id="rId56"/>
-    <hyperlink ref="L30" r:id="rId57"/>
-    <hyperlink ref="L34" r:id="rId58"/>
-    <hyperlink ref="L37" r:id="rId59"/>
-    <hyperlink ref="L51" r:id="rId60"/>
-    <hyperlink ref="L52" r:id="rId61"/>
-    <hyperlink ref="L58" r:id="rId62"/>
-    <hyperlink ref="L28" r:id="rId63"/>
-    <hyperlink ref="L78" r:id="rId64"/>
-    <hyperlink ref="L22" r:id="rId65"/>
-    <hyperlink ref="L26" r:id="rId66"/>
-    <hyperlink ref="L29" r:id="rId67"/>
-    <hyperlink ref="L49" r:id="rId68"/>
-    <hyperlink ref="L75" r:id="rId69"/>
-    <hyperlink ref="L76" r:id="rId70"/>
-    <hyperlink ref="L77" r:id="rId71"/>
+    <hyperlink ref="L25" r:id="rId16"/>
+    <hyperlink ref="L26" r:id="rId17"/>
+    <hyperlink ref="L32" r:id="rId18"/>
+    <hyperlink ref="L33" r:id="rId19"/>
+    <hyperlink ref="L36" r:id="rId20"/>
+    <hyperlink ref="L37" r:id="rId21"/>
+    <hyperlink ref="L39" r:id="rId22"/>
+    <hyperlink ref="L40" r:id="rId23"/>
+    <hyperlink ref="L41" r:id="rId24"/>
+    <hyperlink ref="L42" r:id="rId25"/>
+    <hyperlink ref="L43" r:id="rId26"/>
+    <hyperlink ref="L45" r:id="rId27"/>
+    <hyperlink ref="L46" r:id="rId28"/>
+    <hyperlink ref="L44" r:id="rId29"/>
+    <hyperlink ref="L47" r:id="rId30"/>
+    <hyperlink ref="L49" r:id="rId31"/>
+    <hyperlink ref="L54" r:id="rId32"/>
+    <hyperlink ref="L53" r:id="rId33"/>
+    <hyperlink ref="L52" r:id="rId34"/>
+    <hyperlink ref="L55" r:id="rId35"/>
+    <hyperlink ref="L56" r:id="rId36"/>
+    <hyperlink ref="L58" r:id="rId37"/>
+    <hyperlink ref="L59" r:id="rId38"/>
+    <hyperlink ref="L60" r:id="rId39"/>
+    <hyperlink ref="L61" r:id="rId40"/>
+    <hyperlink ref="L62" r:id="rId41"/>
+    <hyperlink ref="L63" r:id="rId42"/>
+    <hyperlink ref="L64" r:id="rId43"/>
+    <hyperlink ref="L65" r:id="rId44"/>
+    <hyperlink ref="L66" r:id="rId45"/>
+    <hyperlink ref="L67" r:id="rId46"/>
+    <hyperlink ref="L68" r:id="rId47"/>
+    <hyperlink ref="L69" r:id="rId48"/>
+    <hyperlink ref="L70" r:id="rId49"/>
+    <hyperlink ref="L71" r:id="rId50"/>
+    <hyperlink ref="L72" r:id="rId51"/>
+    <hyperlink ref="L73" r:id="rId52"/>
+    <hyperlink ref="L28" r:id="rId53"/>
+    <hyperlink ref="L34" r:id="rId54"/>
+    <hyperlink ref="L31" r:id="rId55"/>
+    <hyperlink ref="L35" r:id="rId56"/>
+    <hyperlink ref="L38" r:id="rId57"/>
+    <hyperlink ref="L50" r:id="rId58"/>
+    <hyperlink ref="L51" r:id="rId59"/>
+    <hyperlink ref="L57" r:id="rId60"/>
+    <hyperlink ref="L29" r:id="rId61"/>
+    <hyperlink ref="L77" r:id="rId62"/>
+    <hyperlink ref="L22" r:id="rId63"/>
+    <hyperlink ref="L27" r:id="rId64"/>
+    <hyperlink ref="L30" r:id="rId65"/>
+    <hyperlink ref="L48" r:id="rId66"/>
+    <hyperlink ref="L74" r:id="rId67"/>
+    <hyperlink ref="L75" r:id="rId68"/>
+    <hyperlink ref="L76" r:id="rId69"/>
+    <hyperlink ref="L24" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId72"/>
-  <drawing r:id="rId73"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId71"/>
+  <drawing r:id="rId72"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -6002,13 +5948,13 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="74"/>
     </row>
     <row r="2" spans="1:15" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -6019,7 +5965,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="38" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="3"/>
@@ -6029,7 +5975,7 @@
       <c r="L2" s="30"/>
       <c r="M2" s="30"/>
       <c r="N2" s="30"/>
-      <c r="O2" s="76"/>
+      <c r="O2" s="77"/>
     </row>
     <row r="3" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -6040,7 +5986,7 @@
       </c>
       <c r="E3" s="26"/>
       <c r="F3" s="39" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="G3" s="28"/>
       <c r="H3" s="29"/>
@@ -6050,7 +5996,7 @@
       <c r="L3" s="23"/>
       <c r="M3" s="23"/>
       <c r="N3" s="23"/>
-      <c r="O3" s="77"/>
+      <c r="O3" s="78"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -6067,7 +6013,7 @@
       <c r="L4" s="23"/>
       <c r="M4" s="23"/>
       <c r="N4" s="23"/>
-      <c r="O4" s="77"/>
+      <c r="O4" s="78"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -6084,7 +6030,7 @@
       <c r="L5" s="33"/>
       <c r="M5" s="33"/>
       <c r="N5" s="33"/>
-      <c r="O5" s="77"/>
+      <c r="O5" s="78"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -6101,7 +6047,7 @@
       <c r="L6" s="33"/>
       <c r="M6" s="33"/>
       <c r="N6" s="33"/>
-      <c r="O6" s="78"/>
+      <c r="O6" s="79"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -6115,37 +6061,37 @@
         <v>20</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="I7" s="40" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -6158,35 +6104,35 @@
         <v>4</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>21</v>
+        <v>403</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I8" s="41" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="J8" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K8" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L8" s="48" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="M8" s="48">
         <f>L8*J8</f>
-        <v>0.64400000000000002</v>
+        <v>0.69</v>
       </c>
       <c r="N8" s="14"/>
       <c r="O8" s="46"/>
@@ -6194,7 +6140,7 @@
     <row r="9" spans="1:15" s="47" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A9" s="45"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B76" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B75" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="22" t="s">
@@ -6204,31 +6150,31 @@
         <v>22</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I9" s="42" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="J9" s="20">
         <v>20</v>
       </c>
       <c r="K9" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L9" s="48" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="M9" s="48">
-        <f t="shared" ref="M9:M76" si="1">L9*J9</f>
+        <f t="shared" ref="M9:M75" si="1">L9*J9</f>
         <v>9.120000000000001</v>
       </c>
       <c r="N9" s="20"/>
@@ -6247,28 +6193,28 @@
         <v>23</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I10" s="41" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="J10" s="14">
         <v>10</v>
       </c>
       <c r="K10" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L10" s="48" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="M10" s="48">
         <f t="shared" si="1"/>
@@ -6290,28 +6236,28 @@
         <v>24</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I11" s="42" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="J11" s="20">
         <v>4</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L11" s="48" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="M11" s="48">
         <f t="shared" si="1"/>
@@ -6333,28 +6279,28 @@
         <v>25</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I12" s="41" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="J12" s="14">
         <v>8</v>
       </c>
       <c r="K12" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L12" s="48" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="M12" s="48">
         <f t="shared" si="1"/>
@@ -6376,28 +6322,28 @@
         <v>26</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I13" s="42" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="J13" s="20">
         <v>2</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L13" s="48" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="M13" s="48">
         <f t="shared" si="1"/>
@@ -6419,28 +6365,28 @@
         <v>27</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="J14" s="14">
         <v>2</v>
       </c>
       <c r="K14" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L14" s="48" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="M14" s="48">
         <f t="shared" si="1"/>
@@ -6462,28 +6408,28 @@
         <v>28</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I15" s="42" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="J15" s="20">
         <v>1</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L15" s="48" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="M15" s="48">
         <f t="shared" si="1"/>
@@ -6505,28 +6451,28 @@
         <v>29</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="J16" s="14">
         <v>11</v>
       </c>
       <c r="K16" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L16" s="48" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="M16" s="48">
         <f t="shared" si="1"/>
@@ -6548,28 +6494,28 @@
         <v>30</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I17" s="42" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="J17" s="20">
         <v>23</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L17" s="48" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="M17" s="48">
         <f t="shared" si="1"/>
@@ -6591,28 +6537,28 @@
         <v>31</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="I18" s="41" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="J18" s="14">
         <v>4</v>
       </c>
       <c r="K18" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L18" s="48" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="M18" s="48">
         <f t="shared" si="1"/>
@@ -6634,28 +6580,28 @@
         <v>32</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I19" s="42" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="J19" s="20">
         <v>2</v>
       </c>
       <c r="K19" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L19" s="48" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="M19" s="48">
         <f t="shared" si="1"/>
@@ -6677,28 +6623,28 @@
         <v>33</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="I20" s="41" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="J20" s="14">
         <v>2</v>
       </c>
       <c r="K20" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L20" s="48" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="M20" s="48">
         <f t="shared" si="1"/>
@@ -6720,28 +6666,28 @@
         <v>34</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I21" s="42" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="J21" s="20">
         <v>1</v>
       </c>
       <c r="K21" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L21" s="48" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="M21" s="48">
         <f t="shared" si="1"/>
@@ -6760,28 +6706,28 @@
         <v>4</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="G22" s="41" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I22" s="41" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="J22" s="14">
         <v>1</v>
       </c>
       <c r="K22" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L22" s="15">
         <v>0.37</v>
@@ -6806,28 +6752,28 @@
         <v>35</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="I23" s="41" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="J23" s="14">
         <v>2</v>
       </c>
       <c r="K23" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L23" s="48" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="M23" s="48">
         <f t="shared" si="1"/>
@@ -6836,179 +6782,179 @@
       <c r="N23" s="14"/>
       <c r="O23" s="46"/>
     </row>
-    <row r="24" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" s="47" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A24" s="45"/>
-      <c r="B24" s="17">
-        <f t="shared" si="0"/>
+      <c r="B24" s="16">
+        <f>ROW(B24) - ROW($B$7)</f>
         <v>17</v>
       </c>
-      <c r="C24" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="G24" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="H24" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="I24" s="42" t="s">
-        <v>281</v>
-      </c>
-      <c r="J24" s="20">
+      <c r="C24" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="E24" s="41" t="s">
+        <v>406</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="G24" s="41" t="s">
+        <v>408</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="I24" s="41" t="s">
+        <v>301</v>
+      </c>
+      <c r="J24" s="14">
         <v>1</v>
       </c>
       <c r="K24" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="L24" s="48" t="s">
-        <v>328</v>
+        <v>368</v>
+      </c>
+      <c r="L24" s="15">
+        <v>0.1</v>
       </c>
       <c r="M24" s="48">
         <f t="shared" si="1"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
+        <v>0.1</v>
+      </c>
+      <c r="N24" s="14"/>
+      <c r="O24" s="46"/>
     </row>
     <row r="25" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="45"/>
-      <c r="B25" s="16">
-        <f>ROW(B25) - ROW($B$7)</f>
+      <c r="B25" s="17">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="I25" s="41" t="s">
-        <v>281</v>
-      </c>
-      <c r="J25" s="14">
-        <v>4</v>
+      <c r="D25" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I25" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="J25" s="20">
+        <v>1</v>
       </c>
       <c r="K25" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L25" s="48" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="M25" s="48">
         <f t="shared" si="1"/>
-        <v>0.92</v>
-      </c>
-      <c r="N25" s="14"/>
-      <c r="O25" s="46"/>
-    </row>
-    <row r="26" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+    </row>
+    <row r="26" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="45"/>
-      <c r="B26" s="17">
-        <f t="shared" si="0"/>
+      <c r="B26" s="16">
+        <f>ROW(B26) - ROW($B$7)</f>
         <v>19</v>
       </c>
-      <c r="C26" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="41" t="s">
-        <v>395</v>
+      <c r="C26" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="G26" s="41" t="s">
-        <v>396</v>
+        <v>144</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>191</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>397</v>
+        <v>233</v>
       </c>
       <c r="I26" s="41" t="s">
-        <v>312</v>
+        <v>272</v>
       </c>
       <c r="J26" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K26" s="44" t="s">
-        <v>380</v>
-      </c>
-      <c r="L26" s="15">
-        <v>0.16089999999999999</v>
+        <v>360</v>
+      </c>
+      <c r="L26" s="48" t="s">
+        <v>318</v>
       </c>
       <c r="M26" s="48">
         <f t="shared" si="1"/>
-        <v>0.16089999999999999</v>
-      </c>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-    </row>
-    <row r="27" spans="1:15" s="47" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+        <v>0.92</v>
+      </c>
+      <c r="N26" s="14"/>
+      <c r="O26" s="46"/>
+    </row>
+    <row r="27" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="45"/>
-      <c r="B27" s="16">
-        <f>ROW(B27) - ROW($B$7)</f>
+      <c r="B27" s="17">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C27" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="14" t="s">
+      <c r="C27" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>383</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="G27" s="41" t="s">
         <v>384</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>199</v>
-      </c>
       <c r="H27" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="I27" s="42" t="s">
-        <v>312</v>
+        <v>385</v>
+      </c>
+      <c r="I27" s="41" t="s">
+        <v>301</v>
       </c>
       <c r="J27" s="14">
         <v>1</v>
       </c>
       <c r="K27" s="44" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="L27" s="15">
-        <v>3.56E-2</v>
+        <v>0.16089999999999999</v>
       </c>
       <c r="M27" s="48">
         <f t="shared" si="1"/>
-        <v>3.56E-2</v>
-      </c>
-      <c r="N27" s="14"/>
-      <c r="O27" s="46"/>
-    </row>
-    <row r="28" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>0.16089999999999999</v>
+      </c>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+    </row>
+    <row r="28" spans="1:15" s="47" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A28" s="45"/>
       <c r="B28" s="16">
         <f>ROW(B28) - ROW($B$7)</f>
@@ -7018,726 +6964,726 @@
         <v>7</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>386</v>
+        <v>97</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>311</v>
+        <v>145</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>385</v>
+        <v>192</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="I28" s="42" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="J28" s="14">
         <v>1</v>
       </c>
       <c r="K28" s="44" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="L28" s="15">
-        <v>0.99</v>
+        <v>3.56E-2</v>
       </c>
       <c r="M28" s="48">
         <f t="shared" si="1"/>
-        <v>0.99</v>
+        <v>3.56E-2</v>
       </c>
       <c r="N28" s="14"/>
       <c r="O28" s="46"/>
     </row>
     <row r="29" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A29" s="45"/>
-      <c r="B29" s="17">
-        <f t="shared" si="0"/>
+      <c r="B29" s="16">
+        <f>ROW(B29) - ROW($B$7)</f>
         <v>22</v>
       </c>
-      <c r="C29" s="22" t="s">
-        <v>398</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E29" s="42" t="s">
-        <v>399</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="G29" s="42" t="s">
-        <v>400</v>
-      </c>
-      <c r="H29" s="20" t="s">
-        <v>401</v>
+      <c r="C29" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>236</v>
       </c>
       <c r="I29" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J29" s="20">
+        <v>301</v>
+      </c>
+      <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L29" s="15">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="M29" s="48">
         <f t="shared" si="1"/>
-        <v>1.05</v>
-      </c>
-      <c r="N29" s="20"/>
-      <c r="O29" s="20"/>
+        <v>0.99</v>
+      </c>
+      <c r="N29" s="14"/>
+      <c r="O29" s="46"/>
     </row>
     <row r="30" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A30" s="45"/>
-      <c r="B30" s="16">
-        <f>ROW(B30) - ROW($B$7)</f>
+      <c r="B30" s="17">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C30" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>103</v>
+      <c r="C30" s="22" t="s">
+        <v>386</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="42" t="s">
+        <v>387</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="I30" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="J30" s="14">
-        <v>2</v>
+        <v>300</v>
+      </c>
+      <c r="G30" s="42" t="s">
+        <v>388</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="I30" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="J30" s="20">
+        <v>1</v>
       </c>
       <c r="K30" s="44" t="s">
-        <v>380</v>
-      </c>
-      <c r="L30" s="48">
-        <v>7.6499999999999999E-2</v>
+        <v>360</v>
+      </c>
+      <c r="L30" s="15">
+        <v>1.05</v>
       </c>
       <c r="M30" s="48">
         <f t="shared" si="1"/>
-        <v>0.153</v>
-      </c>
-      <c r="N30" s="14"/>
-      <c r="O30" s="46"/>
+        <v>1.05</v>
+      </c>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
     </row>
     <row r="31" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="45"/>
-      <c r="B31" s="17">
-        <f t="shared" si="0"/>
+      <c r="B31" s="16">
+        <f>ROW(B31) - ROW($B$7)</f>
         <v>24</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>104</v>
+      <c r="D31" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="H31" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="I31" s="42" t="s">
-        <v>313</v>
-      </c>
-      <c r="J31" s="20">
-        <v>4</v>
+        <v>300</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="I31" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="J31" s="14">
+        <v>2</v>
       </c>
       <c r="K31" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="L31" s="48" t="s">
-        <v>343</v>
+        <v>368</v>
+      </c>
+      <c r="L31" s="48">
+        <v>7.6499999999999999E-2</v>
       </c>
       <c r="M31" s="48">
         <f t="shared" si="1"/>
-        <v>1.66</v>
-      </c>
-      <c r="N31" s="20"/>
-      <c r="O31" s="20"/>
-    </row>
-    <row r="32" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
+        <v>0.153</v>
+      </c>
+      <c r="N31" s="14"/>
+      <c r="O31" s="46"/>
+    </row>
+    <row r="32" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A32" s="45"/>
-      <c r="B32" s="16">
-        <f>ROW(B32) - ROW($B$7)</f>
+      <c r="B32" s="17">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="H32" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="I32" s="41" t="s">
-        <v>312</v>
-      </c>
-      <c r="J32" s="14">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G32" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I32" s="42" t="s">
+        <v>302</v>
+      </c>
+      <c r="J32" s="20">
+        <v>4</v>
       </c>
       <c r="K32" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L32" s="48" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="M32" s="48">
         <f t="shared" si="1"/>
-        <v>0.35</v>
-      </c>
-      <c r="N32" s="14"/>
-      <c r="O32" s="46"/>
+        <v>1.66</v>
+      </c>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
     </row>
     <row r="33" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="45"/>
-      <c r="B33" s="17">
-        <f t="shared" si="0"/>
+      <c r="B33" s="16">
+        <f>ROW(B33) - ROW($B$7)</f>
         <v>26</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D33" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>382</v>
+      <c r="D33" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>100</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="G33" s="20" t="s">
-        <v>381</v>
+        <v>147</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>195</v>
       </c>
       <c r="H33" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="I33" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J33" s="20">
+        <v>238</v>
+      </c>
+      <c r="I33" s="41" t="s">
+        <v>301</v>
+      </c>
+      <c r="J33" s="14">
         <v>1</v>
       </c>
       <c r="K33" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="L33" s="48">
-        <v>0.3</v>
+        <v>360</v>
+      </c>
+      <c r="L33" s="48" t="s">
+        <v>333</v>
       </c>
       <c r="M33" s="48">
         <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="N33" s="14"/>
+      <c r="O33" s="46"/>
+    </row>
+    <row r="34" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="45"/>
+      <c r="B34" s="17">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="G34" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="I34" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="J34" s="20">
+        <v>1</v>
+      </c>
+      <c r="K34" s="44" t="s">
+        <v>360</v>
+      </c>
+      <c r="L34" s="48">
         <v>0.3</v>
-      </c>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-    </row>
-    <row r="34" spans="1:15" s="47" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A34" s="45"/>
-      <c r="B34" s="16">
-        <f>ROW(B34) - ROW($B$7)</f>
-        <v>27</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="I34" s="41" t="s">
-        <v>312</v>
-      </c>
-      <c r="J34" s="14">
-        <v>1</v>
-      </c>
-      <c r="K34" s="44" t="s">
-        <v>380</v>
-      </c>
-      <c r="L34" s="48">
-        <v>0.1661</v>
       </c>
       <c r="M34" s="48">
         <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+    </row>
+    <row r="35" spans="1:15" s="47" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A35" s="45"/>
+      <c r="B35" s="16">
+        <f>ROW(B35) - ROW($B$7)</f>
+        <v>28</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="I35" s="41" t="s">
+        <v>301</v>
+      </c>
+      <c r="J35" s="14">
+        <v>1</v>
+      </c>
+      <c r="K35" s="44" t="s">
+        <v>368</v>
+      </c>
+      <c r="L35" s="48">
         <v>0.1661</v>
-      </c>
-      <c r="N34" s="14"/>
-      <c r="O34" s="46"/>
-    </row>
-    <row r="35" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A35" s="45"/>
-      <c r="B35" s="17">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="C35" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="H35" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="I35" s="41" t="s">
-        <v>312</v>
-      </c>
-      <c r="J35" s="20">
-        <v>1</v>
-      </c>
-      <c r="K35" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="L35" s="48" t="s">
-        <v>345</v>
       </c>
       <c r="M35" s="48">
         <f t="shared" si="1"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="N35" s="20"/>
-      <c r="O35" s="20"/>
-    </row>
-    <row r="36" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
+        <v>0.1661</v>
+      </c>
+      <c r="N35" s="14"/>
+      <c r="O35" s="46"/>
+    </row>
+    <row r="36" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A36" s="45"/>
-      <c r="B36" s="16">
-        <f>ROW(B36) - ROW($B$7)</f>
+      <c r="B36" s="17">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C36" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D36" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>249</v>
+      <c r="D36" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="G36" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>240</v>
       </c>
       <c r="I36" s="41" t="s">
-        <v>312</v>
-      </c>
-      <c r="J36" s="14">
+        <v>301</v>
+      </c>
+      <c r="J36" s="20">
         <v>1</v>
       </c>
       <c r="K36" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L36" s="48" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="M36" s="48">
         <f t="shared" si="1"/>
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="N36" s="14"/>
-      <c r="O36" s="46"/>
-    </row>
-    <row r="37" spans="1:15" s="47" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+    </row>
+    <row r="37" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="45"/>
-      <c r="B37" s="17">
-        <f t="shared" si="0"/>
+      <c r="B37" s="16">
+        <f>ROW(B37) - ROW($B$7)</f>
         <v>30</v>
       </c>
       <c r="C37" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="G37" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="H37" s="20" t="s">
-        <v>250</v>
+      <c r="D37" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>241</v>
       </c>
       <c r="I37" s="41" t="s">
-        <v>312</v>
-      </c>
-      <c r="J37" s="20">
+        <v>301</v>
+      </c>
+      <c r="J37" s="14">
         <v>1</v>
       </c>
       <c r="K37" s="44" t="s">
-        <v>380</v>
-      </c>
-      <c r="L37" s="48">
-        <v>3.0800000000000001E-2</v>
+        <v>360</v>
+      </c>
+      <c r="L37" s="48" t="s">
+        <v>335</v>
       </c>
       <c r="M37" s="48">
         <f t="shared" si="1"/>
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="N37" s="14"/>
+      <c r="O37" s="46"/>
+    </row>
+    <row r="38" spans="1:15" s="47" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A38" s="45"/>
+      <c r="B38" s="17">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="I38" s="41" t="s">
+        <v>301</v>
+      </c>
+      <c r="J38" s="20">
+        <v>1</v>
+      </c>
+      <c r="K38" s="44" t="s">
+        <v>368</v>
+      </c>
+      <c r="L38" s="48">
         <v>3.0800000000000001E-2</v>
-      </c>
-      <c r="N37" s="20"/>
-      <c r="O37" s="20"/>
-    </row>
-    <row r="38" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="45"/>
-      <c r="B38" s="16">
-        <f>ROW(B38) - ROW($B$7)</f>
-        <v>31</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="I38" s="41" t="s">
-        <v>283</v>
-      </c>
-      <c r="J38" s="14">
-        <v>3</v>
-      </c>
-      <c r="K38" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="L38" s="48" t="s">
-        <v>322</v>
       </c>
       <c r="M38" s="48">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="N38" s="14"/>
-      <c r="O38" s="46"/>
-    </row>
-    <row r="39" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="N38" s="20"/>
+      <c r="O38" s="20"/>
+    </row>
+    <row r="39" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="45"/>
-      <c r="B39" s="17">
-        <f t="shared" si="0"/>
+      <c r="B39" s="16">
+        <f>ROW(B39) - ROW($B$7)</f>
         <v>32</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="G39" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="H39" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="I39" s="42" t="s">
-        <v>284</v>
-      </c>
-      <c r="J39" s="20">
-        <v>1</v>
+      <c r="D39" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="H39" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="I39" s="41" t="s">
+        <v>274</v>
+      </c>
+      <c r="J39" s="14">
+        <v>3</v>
       </c>
       <c r="K39" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L39" s="48" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="M39" s="48">
         <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-      <c r="N39" s="20"/>
-      <c r="O39" s="20"/>
-    </row>
-    <row r="40" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="N39" s="14"/>
+      <c r="O39" s="46"/>
+    </row>
+    <row r="40" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A40" s="45"/>
-      <c r="B40" s="16">
-        <f>ROW(B40) - ROW($B$7)</f>
+      <c r="B40" s="17">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C40" s="21" t="s">
+      <c r="C40" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="I40" s="41" t="s">
-        <v>285</v>
-      </c>
-      <c r="J40" s="14">
-        <v>5</v>
+      <c r="D40" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="I40" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="J40" s="20">
+        <v>1</v>
       </c>
       <c r="K40" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L40" s="48" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="M40" s="48">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="N40" s="14"/>
-      <c r="O40" s="46"/>
-    </row>
-    <row r="41" spans="1:15" s="47" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+        <v>0.1</v>
+      </c>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+    </row>
+    <row r="41" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="45"/>
-      <c r="B41" s="17">
-        <f t="shared" si="0"/>
+      <c r="B41" s="16">
+        <f>ROW(B41) - ROW($B$7)</f>
         <v>34</v>
       </c>
-      <c r="C41" s="22" t="s">
+      <c r="C41" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D41" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="F41" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="G41" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="H41" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="I41" s="42" t="s">
-        <v>286</v>
-      </c>
-      <c r="J41" s="20">
-        <v>24</v>
+      <c r="D41" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="I41" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="J41" s="14">
+        <v>6</v>
       </c>
       <c r="K41" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L41" s="48" t="s">
-        <v>347</v>
+        <v>311</v>
       </c>
       <c r="M41" s="48">
         <f t="shared" si="1"/>
-        <v>0.36</v>
-      </c>
-      <c r="N41" s="20"/>
-      <c r="O41" s="20"/>
-    </row>
-    <row r="42" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="N41" s="14"/>
+      <c r="O41" s="46"/>
+    </row>
+    <row r="42" spans="1:15" s="47" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A42" s="45"/>
-      <c r="B42" s="16">
-        <f>ROW(B42) - ROW($B$7)</f>
+      <c r="B42" s="17">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C42" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="F42" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="G42" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="I42" s="41" t="s">
-        <v>287</v>
-      </c>
-      <c r="J42" s="14">
-        <v>1</v>
+      <c r="C42" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="I42" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="J42" s="20">
+        <v>24</v>
       </c>
       <c r="K42" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L42" s="48" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="M42" s="48">
         <f t="shared" si="1"/>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="N42" s="14"/>
-      <c r="O42" s="46"/>
-    </row>
-    <row r="43" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>0.36</v>
+      </c>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
+    </row>
+    <row r="43" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="45"/>
-      <c r="B43" s="17">
-        <f t="shared" si="0"/>
+      <c r="B43" s="16">
+        <f>ROW(B43) - ROW($B$7)</f>
         <v>36</v>
       </c>
-      <c r="C43" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="G43" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="H43" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="I43" s="42" t="s">
-        <v>288</v>
-      </c>
-      <c r="J43" s="20">
+      <c r="C43" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="I43" s="41" t="s">
+        <v>278</v>
+      </c>
+      <c r="J43" s="14">
         <v>1</v>
       </c>
       <c r="K43" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L43" s="48" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="M43" s="48">
         <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-      <c r="N43" s="20"/>
-      <c r="O43" s="20"/>
-    </row>
-    <row r="44" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="N43" s="14"/>
+      <c r="O43" s="46"/>
+    </row>
+    <row r="44" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="45"/>
-      <c r="B44" s="16">
+      <c r="B44" s="17">
         <f>ROW(B44) - ROW($B$7)</f>
         <v>37</v>
       </c>
-      <c r="C44" s="21" t="s">
+      <c r="C44" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D44" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="G44" s="14" t="s">
-        <v>374</v>
+      <c r="D44" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>207</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="I44" s="41" t="s">
-        <v>289</v>
-      </c>
-      <c r="J44" s="14">
-        <v>1</v>
+        <v>231</v>
+      </c>
+      <c r="I44" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="J44" s="20">
+        <v>5</v>
       </c>
       <c r="K44" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L44" s="48" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="M44" s="48">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-      <c r="N44" s="14"/>
-      <c r="O44" s="46"/>
+        <f>L44*J44</f>
+        <v>0.5</v>
+      </c>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
     </row>
     <row r="45" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="45"/>
@@ -7749,31 +7695,31 @@
         <v>12</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I45" s="42" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="J45" s="20">
         <v>1</v>
       </c>
       <c r="K45" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L45" s="48" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="M45" s="48">
         <f t="shared" si="1"/>
@@ -7792,31 +7738,31 @@
         <v>12</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I46" s="41" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="J46" s="14">
         <v>1</v>
       </c>
       <c r="K46" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L46" s="48" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="M46" s="48">
         <f t="shared" si="1"/>
@@ -7825,1292 +7771,1292 @@
       <c r="N46" s="14"/>
       <c r="O46" s="46"/>
     </row>
-    <row r="47" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A47" s="45"/>
-      <c r="B47" s="17">
-        <f t="shared" si="0"/>
+      <c r="B47" s="16">
+        <f>ROW(B47) - ROW($B$7)</f>
         <v>40</v>
       </c>
-      <c r="C47" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="G47" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="H47" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="I47" s="42" t="s">
-        <v>292</v>
-      </c>
-      <c r="J47" s="20">
+      <c r="C47" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="I47" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="J47" s="14">
         <v>4</v>
       </c>
       <c r="K47" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L47" s="48" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="M47" s="48">
         <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
-      <c r="N47" s="20"/>
-      <c r="O47" s="20"/>
-    </row>
-    <row r="48" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="N47" s="14"/>
+      <c r="O47" s="46"/>
+    </row>
+    <row r="48" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="45"/>
       <c r="B48" s="16">
         <f>ROW(B48) - ROW($B$7)</f>
         <v>41</v>
       </c>
-      <c r="C48" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F48" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="G48" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="I48" s="41" t="s">
-        <v>293</v>
-      </c>
-      <c r="J48" s="14">
-        <v>4</v>
+      <c r="C48" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="E48" s="42" t="s">
+        <v>391</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="G48" s="42" t="s">
+        <v>392</v>
+      </c>
+      <c r="H48" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="I48" s="42" t="s">
+        <v>393</v>
+      </c>
+      <c r="J48" s="20">
+        <v>1</v>
       </c>
       <c r="K48" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="L48" s="48" t="s">
-        <v>322</v>
+        <v>360</v>
+      </c>
+      <c r="L48" s="15">
+        <v>0.1</v>
       </c>
       <c r="M48" s="48">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="N48" s="14"/>
       <c r="O48" s="46"/>
     </row>
     <row r="49" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="45"/>
-      <c r="B49" s="16">
-        <f>ROW(B49) - ROW($B$7)</f>
+      <c r="B49" s="17">
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C49" s="22" t="s">
-        <v>12</v>
+      <c r="C49" s="21" t="s">
+        <v>13</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>402</v>
-      </c>
-      <c r="E49" s="42" t="s">
-        <v>403</v>
+        <v>54</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>114</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="G49" s="42" t="s">
-        <v>404</v>
+        <v>152</v>
+      </c>
+      <c r="G49" s="20" t="s">
+        <v>209</v>
       </c>
       <c r="H49" s="20" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I49" s="42" t="s">
-        <v>405</v>
+        <v>283</v>
       </c>
       <c r="J49" s="20">
         <v>1</v>
       </c>
       <c r="K49" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="L49" s="15">
-        <v>0.1</v>
+        <v>360</v>
+      </c>
+      <c r="L49" s="48" t="s">
+        <v>311</v>
       </c>
       <c r="M49" s="48">
         <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
-      <c r="N49" s="14"/>
-      <c r="O49" s="46"/>
-    </row>
-    <row r="50" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N49" s="20"/>
+      <c r="O49" s="20"/>
+    </row>
+    <row r="50" spans="1:15" s="47" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A50" s="45"/>
-      <c r="B50" s="17">
-        <f t="shared" si="0"/>
+      <c r="B50" s="16">
+        <f>ROW(B50) - ROW($B$7)</f>
         <v>43</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="E50" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="F50" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="G50" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="H50" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="I50" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="J50" s="20">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="G50" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="I50" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="J50" s="14">
+        <v>2</v>
       </c>
       <c r="K50" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="L50" s="48" t="s">
-        <v>322</v>
+        <v>368</v>
+      </c>
+      <c r="L50" s="48">
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="M50" s="48">
         <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-      <c r="N50" s="20"/>
-      <c r="O50" s="20"/>
-    </row>
-    <row r="51" spans="1:15" s="47" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+        <v>1.8E-3</v>
+      </c>
+      <c r="N50" s="14"/>
+      <c r="O50" s="46"/>
+    </row>
+    <row r="51" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A51" s="45"/>
-      <c r="B51" s="16">
-        <f>ROW(B51) - ROW($B$7)</f>
+      <c r="B51" s="17">
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="C51" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E51" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="F51" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="G51" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="H51" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="I51" s="41" t="s">
-        <v>295</v>
-      </c>
-      <c r="J51" s="14">
-        <v>2</v>
+      <c r="D51" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="F51" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="G51" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="H51" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="I51" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="J51" s="20">
+        <v>3</v>
       </c>
       <c r="K51" s="44" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="L51" s="48">
-        <v>8.9999999999999998E-4</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="M51" s="48">
         <f t="shared" si="1"/>
-        <v>1.8E-3</v>
-      </c>
-      <c r="N51" s="14"/>
-      <c r="O51" s="46"/>
+        <v>1.26E-2</v>
+      </c>
+      <c r="N51" s="20"/>
+      <c r="O51" s="20"/>
     </row>
     <row r="52" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A52" s="45"/>
-      <c r="B52" s="17">
-        <f t="shared" si="0"/>
+      <c r="B52" s="16">
+        <f>ROW(B52) - ROW($B$7)</f>
         <v>45</v>
       </c>
-      <c r="C52" s="22" t="s">
+      <c r="C52" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D52" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E52" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="F52" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="G52" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="H52" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="I52" s="42" t="s">
-        <v>296</v>
-      </c>
-      <c r="J52" s="20">
-        <v>3</v>
+      <c r="D52" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="H52" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="I52" s="41" t="s">
+        <v>286</v>
+      </c>
+      <c r="J52" s="14">
+        <v>2</v>
       </c>
       <c r="K52" s="44" t="s">
-        <v>380</v>
-      </c>
-      <c r="L52" s="48">
-        <v>4.1999999999999997E-3</v>
+        <v>360</v>
+      </c>
+      <c r="L52" s="48" t="s">
+        <v>314</v>
       </c>
       <c r="M52" s="48">
         <f t="shared" si="1"/>
-        <v>1.26E-2</v>
-      </c>
-      <c r="N52" s="20"/>
-      <c r="O52" s="20"/>
-    </row>
-    <row r="53" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>0.32</v>
+      </c>
+      <c r="N52" s="14"/>
+      <c r="O52" s="46"/>
+    </row>
+    <row r="53" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="45"/>
-      <c r="B53" s="16">
-        <f>ROW(B53) - ROW($B$7)</f>
+      <c r="B53" s="17">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C53" s="21" t="s">
+      <c r="C53" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D53" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="F53" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="G53" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="H53" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="I53" s="41" t="s">
-        <v>297</v>
-      </c>
-      <c r="J53" s="14">
+      <c r="D53" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F53" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="G53" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="H53" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="I53" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="J53" s="20">
         <v>2</v>
       </c>
       <c r="K53" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L53" s="48" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="M53" s="48">
         <f t="shared" si="1"/>
-        <v>0.32</v>
-      </c>
-      <c r="N53" s="14"/>
-      <c r="O53" s="46"/>
+        <v>0.17349999999999999</v>
+      </c>
+      <c r="N53" s="20"/>
+      <c r="O53" s="20"/>
     </row>
     <row r="54" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="45"/>
-      <c r="B54" s="17">
-        <f t="shared" si="0"/>
+      <c r="B54" s="16">
+        <f>ROW(B54) - ROW($B$7)</f>
         <v>47</v>
       </c>
-      <c r="C54" s="22" t="s">
+      <c r="C54" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D54" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="E54" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="F54" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="G54" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="H54" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="I54" s="42" t="s">
-        <v>298</v>
-      </c>
-      <c r="J54" s="20">
-        <v>2</v>
+      <c r="D54" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="H54" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="I54" s="41" t="s">
+        <v>288</v>
+      </c>
+      <c r="J54" s="14">
+        <v>1</v>
       </c>
       <c r="K54" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L54" s="48" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="M54" s="48">
         <f t="shared" si="1"/>
-        <v>0.17349999999999999</v>
-      </c>
-      <c r="N54" s="20"/>
-      <c r="O54" s="20"/>
-    </row>
-    <row r="55" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
+        <v>8.6749999999999994E-2</v>
+      </c>
+      <c r="N54" s="14"/>
+      <c r="O54" s="46"/>
+    </row>
+    <row r="55" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A55" s="45"/>
-      <c r="B55" s="16">
-        <f>ROW(B55) - ROW($B$7)</f>
+      <c r="B55" s="17">
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C55" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E55" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="F55" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="G55" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="H55" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="I55" s="41" t="s">
-        <v>299</v>
-      </c>
-      <c r="J55" s="14">
+      <c r="C55" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="G55" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="H55" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="I55" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="J55" s="20">
         <v>1</v>
       </c>
       <c r="K55" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L55" s="48" t="s">
-        <v>353</v>
+        <v>317</v>
       </c>
       <c r="M55" s="48">
         <f t="shared" si="1"/>
-        <v>8.6749999999999994E-2</v>
-      </c>
-      <c r="N55" s="14"/>
-      <c r="O55" s="46"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="N55" s="20"/>
+      <c r="O55" s="20"/>
     </row>
     <row r="56" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A56" s="45"/>
-      <c r="B56" s="17">
-        <f t="shared" si="0"/>
+      <c r="B56" s="16">
+        <f>ROW(B56) - ROW($B$7)</f>
         <v>49</v>
       </c>
-      <c r="C56" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E56" s="20" t="s">
-        <v>127</v>
+      <c r="C56" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>120</v>
       </c>
       <c r="F56" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="G56" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="H56" s="20" t="s">
-        <v>256</v>
+        <v>300</v>
+      </c>
+      <c r="G56" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="H56" s="14" t="s">
+        <v>248</v>
       </c>
       <c r="I56" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J56" s="20">
-        <v>1</v>
+        <v>301</v>
+      </c>
+      <c r="J56" s="14">
+        <v>2</v>
       </c>
       <c r="K56" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L56" s="48" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="M56" s="48">
         <f t="shared" si="1"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="N56" s="20"/>
-      <c r="O56" s="20"/>
-    </row>
-    <row r="57" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>2.04</v>
+      </c>
+      <c r="N56" s="14"/>
+      <c r="O56" s="46"/>
+    </row>
+    <row r="57" spans="1:15" s="47" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A57" s="45"/>
-      <c r="B57" s="16">
-        <f>ROW(B57) - ROW($B$7)</f>
+      <c r="B57" s="17">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C57" s="21" t="s">
+      <c r="C57" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D57" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E57" s="14" t="s">
-        <v>127</v>
+      <c r="D57" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>121</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="G57" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="H57" s="14" t="s">
-        <v>257</v>
+        <v>300</v>
+      </c>
+      <c r="G57" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="H57" s="20" t="s">
+        <v>249</v>
       </c>
       <c r="I57" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J57" s="14">
-        <v>2</v>
+        <v>301</v>
+      </c>
+      <c r="J57" s="20">
+        <v>3</v>
       </c>
       <c r="K57" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="L57" s="48" t="s">
-        <v>375</v>
+        <v>368</v>
+      </c>
+      <c r="L57" s="48">
+        <v>0.36980000000000002</v>
       </c>
       <c r="M57" s="48">
         <f t="shared" si="1"/>
-        <v>2.04</v>
-      </c>
-      <c r="N57" s="14"/>
-      <c r="O57" s="46"/>
-    </row>
-    <row r="58" spans="1:15" s="47" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+        <v>1.1093999999999999</v>
+      </c>
+      <c r="N57" s="20"/>
+      <c r="O57" s="20"/>
+    </row>
+    <row r="58" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="45"/>
-      <c r="B58" s="17">
-        <f t="shared" si="0"/>
+      <c r="B58" s="16">
+        <f>ROW(B58) - ROW($B$7)</f>
         <v>51</v>
       </c>
-      <c r="C58" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D58" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="E58" s="20" t="s">
-        <v>128</v>
+      <c r="C58" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="D58" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="F58" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="G58" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="H58" s="20" t="s">
-        <v>258</v>
+        <v>300</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="H58" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="I58" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J58" s="20">
-        <v>3</v>
+        <v>301</v>
+      </c>
+      <c r="J58" s="14">
+        <v>1</v>
       </c>
       <c r="K58" s="44" t="s">
-        <v>380</v>
-      </c>
-      <c r="L58" s="48">
-        <v>0.36980000000000002</v>
+        <v>360</v>
+      </c>
+      <c r="L58" s="48" t="s">
+        <v>344</v>
       </c>
       <c r="M58" s="48">
         <f t="shared" si="1"/>
-        <v>1.1093999999999999</v>
-      </c>
-      <c r="N58" s="20"/>
-      <c r="O58" s="20"/>
+        <v>1.67</v>
+      </c>
+      <c r="N58" s="14"/>
+      <c r="O58" s="46"/>
     </row>
     <row r="59" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="45"/>
-      <c r="B59" s="16">
-        <f>ROW(B59) - ROW($B$7)</f>
+      <c r="B59" s="17">
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C59" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>129</v>
+      <c r="C59" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>123</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="G59" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="H59" s="14" t="s">
-        <v>259</v>
+        <v>160</v>
+      </c>
+      <c r="G59" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="H59" s="20" t="s">
+        <v>251</v>
       </c>
       <c r="I59" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J59" s="14">
+        <v>301</v>
+      </c>
+      <c r="J59" s="20">
         <v>1</v>
       </c>
       <c r="K59" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L59" s="48" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="M59" s="48">
         <f t="shared" si="1"/>
-        <v>1.67</v>
-      </c>
-      <c r="N59" s="14"/>
-      <c r="O59" s="46"/>
-    </row>
-    <row r="60" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
+        <v>1.35</v>
+      </c>
+      <c r="N59" s="20"/>
+      <c r="O59" s="20"/>
+    </row>
+    <row r="60" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A60" s="45"/>
-      <c r="B60" s="17">
-        <f t="shared" si="0"/>
+      <c r="B60" s="16">
+        <f>ROW(B60) - ROW($B$7)</f>
         <v>53</v>
       </c>
-      <c r="C60" s="22" t="s">
+      <c r="C60" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E60" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="F60" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="G60" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="H60" s="20" t="s">
-        <v>260</v>
+      <c r="D60" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F60" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G60" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="H60" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="I60" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J60" s="20">
+        <v>301</v>
+      </c>
+      <c r="J60" s="14">
         <v>1</v>
       </c>
       <c r="K60" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L60" s="48" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="M60" s="48">
         <f t="shared" si="1"/>
-        <v>1.35</v>
-      </c>
-      <c r="N60" s="20"/>
-      <c r="O60" s="20"/>
+        <v>3.05</v>
+      </c>
+      <c r="N60" s="14"/>
+      <c r="O60" s="46"/>
     </row>
     <row r="61" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A61" s="45"/>
-      <c r="B61" s="16">
-        <f>ROW(B61) - ROW($B$7)</f>
+      <c r="B61" s="17">
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C61" s="21" t="s">
+      <c r="C61" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D61" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E61" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="F61" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="G61" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="H61" s="14" t="s">
-        <v>261</v>
+      <c r="D61" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G61" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>251</v>
       </c>
       <c r="I61" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J61" s="14">
+        <v>301</v>
+      </c>
+      <c r="J61" s="20">
         <v>1</v>
       </c>
       <c r="K61" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L61" s="48" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="M61" s="48">
         <f t="shared" si="1"/>
-        <v>3.05</v>
-      </c>
-      <c r="N61" s="14"/>
-      <c r="O61" s="46"/>
-    </row>
-    <row r="62" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="N61" s="20"/>
+      <c r="O61" s="20"/>
+    </row>
+    <row r="62" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="45"/>
-      <c r="B62" s="17">
-        <f t="shared" si="0"/>
+      <c r="B62" s="16">
+        <f>ROW(B62) - ROW($B$7)</f>
         <v>55</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="C62" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D62" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E62" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="F62" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="G62" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="H62" s="20" t="s">
-        <v>260</v>
+      <c r="D62" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E62" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="F62" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="G62" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="I62" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J62" s="20">
+        <v>301</v>
+      </c>
+      <c r="J62" s="14">
         <v>1</v>
       </c>
       <c r="K62" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L62" s="48" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="M62" s="48">
         <f t="shared" si="1"/>
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="N62" s="20"/>
-      <c r="O62" s="20"/>
-    </row>
-    <row r="63" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
+        <v>2.74</v>
+      </c>
+      <c r="N62" s="14"/>
+      <c r="O62" s="46"/>
+    </row>
+    <row r="63" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A63" s="45"/>
-      <c r="B63" s="16">
-        <f>ROW(B63) - ROW($B$7)</f>
+      <c r="B63" s="17">
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="C63" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E63" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="F63" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="G63" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="H63" s="14" t="s">
-        <v>260</v>
+      <c r="D63" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="F63" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G63" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="H63" s="20" t="s">
+        <v>251</v>
       </c>
       <c r="I63" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J63" s="14">
+        <v>301</v>
+      </c>
+      <c r="J63" s="20">
         <v>1</v>
       </c>
       <c r="K63" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L63" s="48" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="M63" s="48">
         <f t="shared" si="1"/>
-        <v>2.74</v>
-      </c>
-      <c r="N63" s="14"/>
-      <c r="O63" s="46"/>
+        <v>1.21</v>
+      </c>
+      <c r="N63" s="20"/>
+      <c r="O63" s="20"/>
     </row>
     <row r="64" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A64" s="45"/>
-      <c r="B64" s="17">
-        <f t="shared" si="0"/>
+      <c r="B64" s="16">
+        <f>ROW(B64) - ROW($B$7)</f>
         <v>57</v>
       </c>
       <c r="C64" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D64" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E64" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F64" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="G64" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="H64" s="20" t="s">
-        <v>260</v>
+      <c r="D64" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="F64" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="G64" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="H64" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="I64" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J64" s="20">
+        <v>301</v>
+      </c>
+      <c r="J64" s="14">
         <v>1</v>
       </c>
       <c r="K64" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L64" s="48" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="M64" s="48">
         <f t="shared" si="1"/>
-        <v>1.21</v>
-      </c>
-      <c r="N64" s="20"/>
-      <c r="O64" s="20"/>
-    </row>
-    <row r="65" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>0.61</v>
+      </c>
+      <c r="N64" s="14"/>
+      <c r="O64" s="46"/>
+    </row>
+    <row r="65" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="45"/>
-      <c r="B65" s="16">
-        <f>ROW(B65) - ROW($B$7)</f>
+      <c r="B65" s="17">
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C65" s="21" t="s">
+      <c r="C65" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D65" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E65" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="F65" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="G65" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="H65" s="14" t="s">
-        <v>262</v>
+      <c r="D65" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="F65" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="G65" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="H65" s="20" t="s">
+        <v>254</v>
       </c>
       <c r="I65" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J65" s="14">
+        <v>301</v>
+      </c>
+      <c r="J65" s="20">
         <v>1</v>
       </c>
       <c r="K65" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L65" s="48" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="M65" s="48">
         <f t="shared" si="1"/>
-        <v>0.61</v>
-      </c>
-      <c r="N65" s="14"/>
-      <c r="O65" s="46"/>
+        <v>0.41</v>
+      </c>
+      <c r="N65" s="20"/>
+      <c r="O65" s="20"/>
     </row>
     <row r="66" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="45"/>
-      <c r="B66" s="17">
-        <f t="shared" si="0"/>
+      <c r="B66" s="16">
+        <f>ROW(B66) - ROW($B$7)</f>
         <v>59</v>
       </c>
-      <c r="C66" s="22" t="s">
+      <c r="C66" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D66" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E66" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="F66" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="G66" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="H66" s="20" t="s">
-        <v>263</v>
+      <c r="D66" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E66" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="F66" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G66" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="H66" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="I66" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J66" s="20">
+        <v>301</v>
+      </c>
+      <c r="J66" s="14">
         <v>1</v>
       </c>
       <c r="K66" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L66" s="48" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M66" s="48">
         <f t="shared" si="1"/>
-        <v>0.41</v>
-      </c>
-      <c r="N66" s="20"/>
-      <c r="O66" s="20"/>
+        <v>0.4</v>
+      </c>
+      <c r="N66" s="14"/>
+      <c r="O66" s="46"/>
     </row>
     <row r="67" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="45"/>
-      <c r="B67" s="16">
-        <f>ROW(B67) - ROW($B$7)</f>
+      <c r="B67" s="17">
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C67" s="21" t="s">
+      <c r="C67" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D67" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E67" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="F67" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="G67" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="H67" s="14" t="s">
-        <v>263</v>
+      <c r="D67" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="F67" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G67" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="H67" s="20" t="s">
+        <v>251</v>
       </c>
       <c r="I67" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J67" s="14">
+        <v>301</v>
+      </c>
+      <c r="J67" s="20">
         <v>1</v>
       </c>
       <c r="K67" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L67" s="48" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="M67" s="48">
         <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-      <c r="N67" s="14"/>
-      <c r="O67" s="46"/>
-    </row>
-    <row r="68" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
+        <v>6.21</v>
+      </c>
+      <c r="N67" s="20"/>
+      <c r="O67" s="20"/>
+    </row>
+    <row r="68" spans="1:15" s="47" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A68" s="45"/>
-      <c r="B68" s="17">
-        <f t="shared" si="0"/>
+      <c r="B68" s="16">
+        <f>ROW(B68) - ROW($B$7)</f>
         <v>61</v>
       </c>
-      <c r="C68" s="22" t="s">
+      <c r="C68" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E68" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="F68" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="G68" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="H68" s="20" t="s">
-        <v>260</v>
+      <c r="D68" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E68" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="F68" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="G68" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="H68" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="I68" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J68" s="20">
+        <v>301</v>
+      </c>
+      <c r="J68" s="14">
         <v>1</v>
       </c>
       <c r="K68" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L68" s="48" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="M68" s="48">
         <f t="shared" si="1"/>
-        <v>6.21</v>
-      </c>
-      <c r="N68" s="20"/>
-      <c r="O68" s="20"/>
-    </row>
-    <row r="69" spans="1:15" s="47" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+        <v>37.989130000000003</v>
+      </c>
+      <c r="N68" s="14"/>
+      <c r="O68" s="46"/>
+    </row>
+    <row r="69" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A69" s="45"/>
-      <c r="B69" s="16">
-        <f>ROW(B69) - ROW($B$7)</f>
+      <c r="B69" s="17">
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C69" s="21" t="s">
+      <c r="C69" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D69" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="E69" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="F69" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="G69" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="H69" s="14" t="s">
-        <v>260</v>
+      <c r="D69" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F69" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="G69" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="H69" s="20" t="s">
+        <v>255</v>
       </c>
       <c r="I69" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J69" s="14">
+        <v>301</v>
+      </c>
+      <c r="J69" s="20">
         <v>1</v>
       </c>
       <c r="K69" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L69" s="48" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="M69" s="48">
         <f t="shared" si="1"/>
-        <v>37.989130000000003</v>
-      </c>
-      <c r="N69" s="14"/>
-      <c r="O69" s="46"/>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="N69" s="20"/>
+      <c r="O69" s="20"/>
     </row>
     <row r="70" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A70" s="45"/>
-      <c r="B70" s="17">
-        <f t="shared" si="0"/>
+      <c r="B70" s="16">
+        <f>ROW(B70) - ROW($B$7)</f>
         <v>63</v>
       </c>
-      <c r="C70" s="22" t="s">
+      <c r="C70" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D70" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="E70" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="F70" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="G70" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="H70" s="20" t="s">
-        <v>264</v>
+      <c r="D70" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E70" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F70" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="G70" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="H70" s="14" t="s">
+        <v>256</v>
       </c>
       <c r="I70" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J70" s="20">
+        <v>301</v>
+      </c>
+      <c r="J70" s="14">
         <v>1</v>
       </c>
       <c r="K70" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L70" s="48" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="M70" s="48">
         <f t="shared" si="1"/>
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="N70" s="20"/>
-      <c r="O70" s="20"/>
-    </row>
-    <row r="71" spans="1:15" s="47" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>6.19</v>
+      </c>
+      <c r="N70" s="14"/>
+      <c r="O70" s="46"/>
+    </row>
+    <row r="71" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="45"/>
-      <c r="B71" s="16">
-        <f>ROW(B71) - ROW($B$7)</f>
+      <c r="B71" s="17">
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C71" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="E71" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="F71" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="G71" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="H71" s="14" t="s">
-        <v>265</v>
+      <c r="C71" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="F71" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G71" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="H71" s="20" t="s">
+        <v>240</v>
       </c>
       <c r="I71" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="J71" s="14">
+        <v>289</v>
+      </c>
+      <c r="J71" s="20">
         <v>1</v>
       </c>
       <c r="K71" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L71" s="48" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="M71" s="48">
         <f t="shared" si="1"/>
-        <v>6.19</v>
-      </c>
-      <c r="N71" s="14"/>
-      <c r="O71" s="46"/>
+        <v>0.76</v>
+      </c>
+      <c r="N71" s="20"/>
+      <c r="O71" s="20"/>
     </row>
     <row r="72" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="45"/>
-      <c r="B72" s="17">
-        <f t="shared" si="0"/>
+      <c r="B72" s="16">
+        <f>ROW(B72) - ROW($B$7)</f>
         <v>65</v>
       </c>
-      <c r="C72" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D72" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E72" s="20" t="s">
-        <v>141</v>
+      <c r="C72" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E72" s="14" t="s">
+        <v>135</v>
       </c>
       <c r="F72" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="G72" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="H72" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="I72" s="42" t="s">
         <v>300</v>
       </c>
-      <c r="J72" s="20">
+      <c r="G72" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="H72" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="I72" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="J72" s="14">
         <v>1</v>
       </c>
       <c r="K72" s="44" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="L72" s="48" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="M72" s="48">
         <f t="shared" si="1"/>
-        <v>0.76</v>
-      </c>
-      <c r="N72" s="20"/>
-      <c r="O72" s="20"/>
-    </row>
-    <row r="73" spans="1:15" s="47" customFormat="1" x14ac:dyDescent="0.25">
+        <v>0.46</v>
+      </c>
+      <c r="N72" s="14"/>
+      <c r="O72" s="46"/>
+    </row>
+    <row r="73" spans="1:15" s="47" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="45"/>
-      <c r="B73" s="16">
-        <f>ROW(B73) - ROW($B$7)</f>
+      <c r="B73" s="43">
+        <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C73" s="21" t="s">
+      <c r="C73" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D73" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E73" s="14" t="s">
-        <v>142</v>
+      <c r="D73" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>136</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="G73" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="H73" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="I73" s="41" t="s">
-        <v>301</v>
-      </c>
-      <c r="J73" s="14">
+        <v>173</v>
+      </c>
+      <c r="G73" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="H73" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="I73" s="42" t="s">
+        <v>291</v>
+      </c>
+      <c r="J73" s="20">
         <v>1</v>
       </c>
-      <c r="K73" s="44" t="s">
-        <v>371</v>
-      </c>
-      <c r="L73" s="48" t="s">
-        <v>369</v>
-      </c>
-      <c r="M73" s="48">
+      <c r="K73" s="50" t="s">
+        <v>360</v>
+      </c>
+      <c r="L73" s="51" t="s">
+        <v>359</v>
+      </c>
+      <c r="M73" s="51">
         <f t="shared" si="1"/>
-        <v>0.46</v>
-      </c>
-      <c r="N73" s="14"/>
-      <c r="O73" s="46"/>
-    </row>
-    <row r="74" spans="1:15" s="47" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.63</v>
+      </c>
+      <c r="N73" s="20"/>
+      <c r="O73" s="20"/>
+    </row>
+    <row r="74" spans="1:15" s="47" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="45"/>
       <c r="B74" s="43">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="C74" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D74" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E74" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="F74" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="G74" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="H74" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="I74" s="42" t="s">
-        <v>302</v>
-      </c>
-      <c r="J74" s="20">
+      <c r="C74" s="52" t="s">
+        <v>375</v>
+      </c>
+      <c r="D74" s="53" t="s">
+        <v>301</v>
+      </c>
+      <c r="E74" s="68" t="s">
+        <v>394</v>
+      </c>
+      <c r="F74" s="67" t="s">
+        <v>300</v>
+      </c>
+      <c r="G74" s="68" t="s">
+        <v>395</v>
+      </c>
+      <c r="H74" s="67" t="s">
+        <v>396</v>
+      </c>
+      <c r="I74" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="J74" s="67">
         <v>1</v>
       </c>
-      <c r="K74" s="50" t="s">
-        <v>371</v>
-      </c>
-      <c r="L74" s="51" t="s">
-        <v>370</v>
-      </c>
-      <c r="M74" s="51">
+      <c r="K74" s="69" t="s">
+        <v>360</v>
+      </c>
+      <c r="L74" s="58">
+        <v>2.31</v>
+      </c>
+      <c r="M74" s="58">
         <f t="shared" si="1"/>
-        <v>0.63</v>
-      </c>
-      <c r="N74" s="20"/>
-      <c r="O74" s="20"/>
-    </row>
-    <row r="75" spans="1:15" s="47" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.31</v>
+      </c>
+      <c r="N74" s="59"/>
+      <c r="O74" s="59"/>
+    </row>
+    <row r="75" spans="1:15" s="47" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="45"/>
       <c r="B75" s="43">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C75" s="52" t="s">
-        <v>387</v>
-      </c>
-      <c r="D75" s="53" t="s">
-        <v>312</v>
+      <c r="C75" s="66" t="s">
+        <v>375</v>
+      </c>
+      <c r="D75" s="67" t="s">
+        <v>301</v>
       </c>
       <c r="E75" s="68" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="F75" s="67" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="G75" s="68" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="H75" s="67" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="I75" s="68" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="J75" s="67">
         <v>1</v>
       </c>
       <c r="K75" s="69" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="L75" s="58">
-        <v>2.31</v>
+        <v>60</v>
       </c>
       <c r="M75" s="58">
         <f t="shared" si="1"/>
-        <v>2.31</v>
-      </c>
-      <c r="N75" s="59"/>
-      <c r="O75" s="59"/>
-    </row>
-    <row r="76" spans="1:15" s="47" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="N75" s="53"/>
+      <c r="O75" s="53"/>
+    </row>
+    <row r="76" spans="1:15" s="47" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="45"/>
       <c r="B76" s="43">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B76" si="2">ROW(B76) - ROW($B$7)</f>
         <v>69</v>
       </c>
-      <c r="C76" s="66" t="s">
-        <v>387</v>
-      </c>
-      <c r="D76" s="67" t="s">
-        <v>312</v>
-      </c>
-      <c r="E76" s="68" t="s">
-        <v>409</v>
+      <c r="C76" s="52" t="s">
+        <v>375</v>
+      </c>
+      <c r="D76" s="59" t="s">
+        <v>301</v>
+      </c>
+      <c r="E76" s="72" t="s">
+        <v>400</v>
       </c>
       <c r="F76" s="67" t="s">
-        <v>311</v>
-      </c>
-      <c r="G76" s="68" t="s">
-        <v>410</v>
-      </c>
-      <c r="H76" s="67" t="s">
-        <v>411</v>
-      </c>
-      <c r="I76" s="68" t="s">
-        <v>312</v>
-      </c>
-      <c r="J76" s="67">
+        <v>300</v>
+      </c>
+      <c r="G76" s="72" t="s">
+        <v>401</v>
+      </c>
+      <c r="H76" s="59" t="s">
+        <v>402</v>
+      </c>
+      <c r="I76" s="72" t="s">
+        <v>301</v>
+      </c>
+      <c r="J76" s="59">
         <v>1</v>
       </c>
       <c r="K76" s="69" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="L76" s="58">
-        <v>60</v>
+        <v>5.59</v>
       </c>
       <c r="M76" s="58">
-        <f t="shared" si="1"/>
-        <v>60</v>
+        <f t="shared" ref="M76" si="3">L76*J76</f>
+        <v>5.59</v>
       </c>
       <c r="N76" s="53"/>
       <c r="O76" s="53"/>
@@ -9118,116 +9064,73 @@
     <row r="77" spans="1:15" s="47" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="45"/>
       <c r="B77" s="43">
-        <f t="shared" ref="B77" si="2">ROW(B77) - ROW($B$7)</f>
+        <f t="shared" ref="B77" si="4">ROW(B77) - ROW($B$7)</f>
         <v>70</v>
       </c>
-      <c r="C77" s="52" t="s">
-        <v>387</v>
-      </c>
-      <c r="D77" s="59" t="s">
-        <v>312</v>
-      </c>
-      <c r="E77" s="79" t="s">
-        <v>412</v>
-      </c>
-      <c r="F77" s="67" t="s">
-        <v>311</v>
-      </c>
-      <c r="G77" s="79" t="s">
-        <v>413</v>
-      </c>
-      <c r="H77" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="I77" s="79" t="s">
-        <v>312</v>
-      </c>
-      <c r="J77" s="59">
+      <c r="C77" s="54" t="s">
+        <v>375</v>
+      </c>
+      <c r="D77" s="55" t="s">
+        <v>301</v>
+      </c>
+      <c r="E77" s="56" t="s">
+        <v>376</v>
+      </c>
+      <c r="F77" s="55" t="s">
+        <v>301</v>
+      </c>
+      <c r="G77" s="56" t="s">
+        <v>377</v>
+      </c>
+      <c r="H77" s="55" t="s">
+        <v>301</v>
+      </c>
+      <c r="I77" s="56" t="s">
+        <v>301</v>
+      </c>
+      <c r="J77" s="55">
         <v>1</v>
       </c>
-      <c r="K77" s="69" t="s">
-        <v>414</v>
-      </c>
-      <c r="L77" s="58">
-        <v>5.59</v>
+      <c r="K77" s="57" t="s">
+        <v>378</v>
+      </c>
+      <c r="L77" s="60">
+        <v>6.8</v>
       </c>
       <c r="M77" s="58">
-        <f t="shared" ref="M77" si="3">L77*J77</f>
-        <v>5.59</v>
-      </c>
-      <c r="N77" s="53"/>
-      <c r="O77" s="53"/>
-    </row>
-    <row r="78" spans="1:15" s="47" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="45"/>
-      <c r="B78" s="43">
-        <f t="shared" ref="B78" si="4">ROW(B78) - ROW($B$7)</f>
-        <v>71</v>
-      </c>
-      <c r="C78" s="54" t="s">
-        <v>387</v>
-      </c>
-      <c r="D78" s="55" t="s">
-        <v>312</v>
-      </c>
-      <c r="E78" s="56" t="s">
-        <v>388</v>
-      </c>
-      <c r="F78" s="55" t="s">
-        <v>312</v>
-      </c>
-      <c r="G78" s="56" t="s">
-        <v>389</v>
-      </c>
-      <c r="H78" s="55" t="s">
-        <v>312</v>
-      </c>
-      <c r="I78" s="56" t="s">
-        <v>312</v>
-      </c>
-      <c r="J78" s="55">
-        <v>1</v>
-      </c>
-      <c r="K78" s="57" t="s">
-        <v>390</v>
-      </c>
-      <c r="L78" s="60">
+        <f t="shared" ref="M77" si="5">L77*J77</f>
         <v>6.8</v>
       </c>
-      <c r="M78" s="58">
-        <f t="shared" ref="M78" si="5">L78*J78</f>
-        <v>6.8</v>
-      </c>
-      <c r="N78" s="61"/>
-      <c r="O78" s="61"/>
-    </row>
-    <row r="79" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
-      <c r="K79" s="74" t="s">
-        <v>377</v>
-      </c>
-      <c r="L79" s="75"/>
-      <c r="M79" s="49">
-        <f>SUM(M8:M78)</f>
-        <v>182.30258000000001</v>
-      </c>
-      <c r="N79" s="1"/>
-      <c r="O79" s="1"/>
+      <c r="N77" s="61"/>
+      <c r="O77" s="61"/>
+    </row>
+    <row r="78" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="75" t="s">
+        <v>365</v>
+      </c>
+      <c r="L78" s="76"/>
+      <c r="M78" s="49">
+        <f>SUM(M8:M77)</f>
+        <v>182.44858000000002</v>
+      </c>
+      <c r="N78" s="1"/>
+      <c r="O78" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="O2:O6"/>
-    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="K78:L78"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="K8" r:id="rId1"/>
@@ -9245,64 +9148,63 @@
     <hyperlink ref="K20" r:id="rId13"/>
     <hyperlink ref="K21" r:id="rId14"/>
     <hyperlink ref="K23" r:id="rId15"/>
-    <hyperlink ref="K24" r:id="rId16"/>
-    <hyperlink ref="K25" r:id="rId17"/>
-    <hyperlink ref="K31" r:id="rId18"/>
-    <hyperlink ref="K32" r:id="rId19"/>
-    <hyperlink ref="K35" r:id="rId20"/>
-    <hyperlink ref="K36" r:id="rId21"/>
-    <hyperlink ref="K38" r:id="rId22"/>
-    <hyperlink ref="K39" r:id="rId23"/>
-    <hyperlink ref="K40" r:id="rId24"/>
-    <hyperlink ref="K41" r:id="rId25"/>
-    <hyperlink ref="K42" r:id="rId26"/>
-    <hyperlink ref="K43" r:id="rId27"/>
-    <hyperlink ref="K44" r:id="rId28"/>
-    <hyperlink ref="K45" r:id="rId29"/>
-    <hyperlink ref="K46" r:id="rId30"/>
-    <hyperlink ref="K47" r:id="rId31"/>
-    <hyperlink ref="K48" r:id="rId32"/>
-    <hyperlink ref="K50" r:id="rId33"/>
-    <hyperlink ref="K55" r:id="rId34"/>
-    <hyperlink ref="K54" r:id="rId35"/>
-    <hyperlink ref="K53" r:id="rId36"/>
-    <hyperlink ref="K56" r:id="rId37"/>
-    <hyperlink ref="K57" r:id="rId38"/>
-    <hyperlink ref="K59" r:id="rId39"/>
-    <hyperlink ref="K60" r:id="rId40"/>
-    <hyperlink ref="K61" r:id="rId41"/>
-    <hyperlink ref="K62" r:id="rId42"/>
-    <hyperlink ref="K63" r:id="rId43"/>
-    <hyperlink ref="K64" r:id="rId44"/>
-    <hyperlink ref="K65" r:id="rId45"/>
-    <hyperlink ref="K66" r:id="rId46"/>
-    <hyperlink ref="K67" r:id="rId47"/>
-    <hyperlink ref="K68" r:id="rId48"/>
-    <hyperlink ref="K69" r:id="rId49"/>
-    <hyperlink ref="K70" r:id="rId50"/>
-    <hyperlink ref="K71" r:id="rId51"/>
-    <hyperlink ref="K72" r:id="rId52"/>
-    <hyperlink ref="K73" r:id="rId53"/>
-    <hyperlink ref="K74" r:id="rId54"/>
-    <hyperlink ref="K33" r:id="rId55"/>
-    <hyperlink ref="K27" r:id="rId56"/>
-    <hyperlink ref="K30" r:id="rId57"/>
-    <hyperlink ref="K34" r:id="rId58"/>
-    <hyperlink ref="K37" r:id="rId59"/>
-    <hyperlink ref="K51" r:id="rId60"/>
-    <hyperlink ref="K52" r:id="rId61"/>
-    <hyperlink ref="K58" r:id="rId62"/>
-    <hyperlink ref="K28" r:id="rId63"/>
-    <hyperlink ref="K78" r:id="rId64"/>
-    <hyperlink ref="K76" r:id="rId65"/>
-    <hyperlink ref="K77" r:id="rId66"/>
-    <hyperlink ref="K75" r:id="rId67"/>
-    <hyperlink ref="K49" r:id="rId68"/>
-    <hyperlink ref="K29" r:id="rId69"/>
-    <hyperlink ref="K26" r:id="rId70"/>
-    <hyperlink ref="K22" r:id="rId71"/>
+    <hyperlink ref="K25" r:id="rId16"/>
+    <hyperlink ref="K26" r:id="rId17"/>
+    <hyperlink ref="K32" r:id="rId18"/>
+    <hyperlink ref="K33" r:id="rId19"/>
+    <hyperlink ref="K36" r:id="rId20"/>
+    <hyperlink ref="K37" r:id="rId21"/>
+    <hyperlink ref="K39" r:id="rId22"/>
+    <hyperlink ref="K40" r:id="rId23"/>
+    <hyperlink ref="K41" r:id="rId24"/>
+    <hyperlink ref="K42" r:id="rId25"/>
+    <hyperlink ref="K43" r:id="rId26"/>
+    <hyperlink ref="K45" r:id="rId27"/>
+    <hyperlink ref="K46" r:id="rId28"/>
+    <hyperlink ref="K44" r:id="rId29"/>
+    <hyperlink ref="K47" r:id="rId30"/>
+    <hyperlink ref="K49" r:id="rId31"/>
+    <hyperlink ref="K54" r:id="rId32"/>
+    <hyperlink ref="K53" r:id="rId33"/>
+    <hyperlink ref="K52" r:id="rId34"/>
+    <hyperlink ref="K55" r:id="rId35"/>
+    <hyperlink ref="K56" r:id="rId36"/>
+    <hyperlink ref="K58" r:id="rId37"/>
+    <hyperlink ref="K59" r:id="rId38"/>
+    <hyperlink ref="K60" r:id="rId39"/>
+    <hyperlink ref="K61" r:id="rId40"/>
+    <hyperlink ref="K62" r:id="rId41"/>
+    <hyperlink ref="K63" r:id="rId42"/>
+    <hyperlink ref="K64" r:id="rId43"/>
+    <hyperlink ref="K65" r:id="rId44"/>
+    <hyperlink ref="K66" r:id="rId45"/>
+    <hyperlink ref="K67" r:id="rId46"/>
+    <hyperlink ref="K68" r:id="rId47"/>
+    <hyperlink ref="K69" r:id="rId48"/>
+    <hyperlink ref="K70" r:id="rId49"/>
+    <hyperlink ref="K71" r:id="rId50"/>
+    <hyperlink ref="K72" r:id="rId51"/>
+    <hyperlink ref="K73" r:id="rId52"/>
+    <hyperlink ref="K34" r:id="rId53"/>
+    <hyperlink ref="K28" r:id="rId54"/>
+    <hyperlink ref="K31" r:id="rId55"/>
+    <hyperlink ref="K35" r:id="rId56"/>
+    <hyperlink ref="K38" r:id="rId57"/>
+    <hyperlink ref="K50" r:id="rId58"/>
+    <hyperlink ref="K51" r:id="rId59"/>
+    <hyperlink ref="K57" r:id="rId60"/>
+    <hyperlink ref="K29" r:id="rId61"/>
+    <hyperlink ref="K77" r:id="rId62"/>
+    <hyperlink ref="K75" r:id="rId63"/>
+    <hyperlink ref="K76" r:id="rId64"/>
+    <hyperlink ref="K74" r:id="rId65"/>
+    <hyperlink ref="K48" r:id="rId66"/>
+    <hyperlink ref="K30" r:id="rId67"/>
+    <hyperlink ref="K27" r:id="rId68"/>
+    <hyperlink ref="K22" r:id="rId69"/>
+    <hyperlink ref="K24" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId72"/>
+  <drawing r:id="rId71"/>
 </worksheet>
 </file>
--- a/Design Files/MainBoard_2.0/Main_Board_2.0/BOM/eSpark-BOM_Main_Board_2.0.xlsx
+++ b/Design Files/MainBoard_2.0/Main_Board_2.0/BOM/eSpark-BOM_Main_Board_2.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="414">
   <si>
     <t>Component list</t>
   </si>
@@ -1259,6 +1259,9 @@
   </si>
   <si>
     <t>R12, R18, R19, R20, R39</t>
+  </si>
+  <si>
+    <t>A10SR10SR30K102A</t>
   </si>
 </sst>
 </file>
@@ -8951,7 +8954,7 @@
         <v>300</v>
       </c>
       <c r="G74" s="68" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="H74" s="67" t="s">
         <v>396</v>
@@ -9197,12 +9200,12 @@
     <hyperlink ref="K77" r:id="rId62"/>
     <hyperlink ref="K75" r:id="rId63"/>
     <hyperlink ref="K76" r:id="rId64"/>
-    <hyperlink ref="K74" r:id="rId65"/>
-    <hyperlink ref="K48" r:id="rId66"/>
-    <hyperlink ref="K30" r:id="rId67"/>
-    <hyperlink ref="K27" r:id="rId68"/>
-    <hyperlink ref="K22" r:id="rId69"/>
-    <hyperlink ref="K24" r:id="rId70"/>
+    <hyperlink ref="K48" r:id="rId65"/>
+    <hyperlink ref="K30" r:id="rId66"/>
+    <hyperlink ref="K27" r:id="rId67"/>
+    <hyperlink ref="K22" r:id="rId68"/>
+    <hyperlink ref="K24" r:id="rId69"/>
+    <hyperlink ref="K74" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId71"/>
